--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118505861</v>
+        <v>118505747</v>
       </c>
       <c r="B2" t="n">
-        <v>91783</v>
+        <v>89575</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700446</v>
+        <v>700420</v>
       </c>
       <c r="R2" t="n">
-        <v>7283484</v>
+        <v>7283482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118505747</v>
+        <v>118505861</v>
       </c>
       <c r="B3" t="n">
-        <v>89575</v>
+        <v>91783</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700420</v>
+        <v>700446</v>
       </c>
       <c r="R3" t="n">
-        <v>7283482</v>
+        <v>7283484</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118505747</v>
       </c>
       <c r="B2" t="n">
-        <v>89575</v>
+        <v>89582</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>118505861</v>
       </c>
       <c r="B3" t="n">
-        <v>91783</v>
+        <v>91790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118505747</v>
+        <v>118505861</v>
       </c>
       <c r="B2" t="n">
-        <v>89582</v>
+        <v>91790</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700420</v>
+        <v>700446</v>
       </c>
       <c r="R2" t="n">
-        <v>7283482</v>
+        <v>7283484</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118505861</v>
+        <v>118505747</v>
       </c>
       <c r="B3" t="n">
-        <v>91790</v>
+        <v>89582</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700446</v>
+        <v>700420</v>
       </c>
       <c r="R3" t="n">
-        <v>7283484</v>
+        <v>7283482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119670372</v>
+        <v>119669271</v>
       </c>
       <c r="B6" t="n">
-        <v>91883</v>
+        <v>91834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700297</v>
+        <v>700583</v>
       </c>
       <c r="R6" t="n">
-        <v>7283911</v>
+        <v>7283727</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,11 +1198,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>under gammal tallåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119669271</v>
+        <v>119668966</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,24 +1241,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1277,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700583</v>
+        <v>700497</v>
       </c>
       <c r="R7" t="n">
-        <v>7283727</v>
+        <v>7283615</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119668966</v>
+        <v>119671451</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,28 +1355,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1391,10 +1386,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700497</v>
+        <v>700295</v>
       </c>
       <c r="R8" t="n">
-        <v>7283615</v>
+        <v>7283983</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119671451</v>
+        <v>119670372</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700295</v>
+        <v>700297</v>
       </c>
       <c r="R9" t="n">
-        <v>7283983</v>
+        <v>7283911</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>under gammal tallåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -5194,10 +5194,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119668423</v>
+        <v>119668910</v>
       </c>
       <c r="B43" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5210,21 +5210,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5241,10 +5241,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700431</v>
+        <v>700502</v>
       </c>
       <c r="R43" t="n">
-        <v>7283462</v>
+        <v>7283590</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5304,10 +5304,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119670767</v>
+        <v>119668926</v>
       </c>
       <c r="B44" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5320,21 +5320,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700279</v>
+        <v>700502</v>
       </c>
       <c r="R44" t="n">
-        <v>7283983</v>
+        <v>7283590</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5414,10 +5414,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119668926</v>
+        <v>119668423</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5430,21 +5430,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>700502</v>
+        <v>700431</v>
       </c>
       <c r="R45" t="n">
-        <v>7283590</v>
+        <v>7283462</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5524,10 +5524,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119668910</v>
+        <v>119670767</v>
       </c>
       <c r="B46" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5540,21 +5540,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700502</v>
+        <v>700279</v>
       </c>
       <c r="R46" t="n">
-        <v>7283590</v>
+        <v>7283983</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -13563,10 +13563,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119670144</v>
+        <v>119668715</v>
       </c>
       <c r="B119" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13575,25 +13575,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13610,10 +13610,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>700448</v>
+        <v>700480</v>
       </c>
       <c r="R119" t="n">
-        <v>7283840</v>
+        <v>7283480</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13673,10 +13673,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119670580</v>
+        <v>119670645</v>
       </c>
       <c r="B120" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13685,25 +13685,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13720,10 +13720,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>700268</v>
+        <v>700279</v>
       </c>
       <c r="R120" t="n">
-        <v>7283948</v>
+        <v>7283952</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13783,7 +13783,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119668715</v>
+        <v>119669683</v>
       </c>
       <c r="B121" t="n">
         <v>91840</v>
@@ -13830,10 +13830,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>700480</v>
+        <v>700488</v>
       </c>
       <c r="R121" t="n">
-        <v>7283480</v>
+        <v>7283816</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13893,7 +13893,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119670645</v>
+        <v>119669143</v>
       </c>
       <c r="B122" t="n">
         <v>91840</v>
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>700279</v>
+        <v>700542</v>
       </c>
       <c r="R122" t="n">
-        <v>7283952</v>
+        <v>7283681</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14003,10 +14003,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119669683</v>
+        <v>119670746</v>
       </c>
       <c r="B123" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14015,25 +14015,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14050,10 +14050,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>700488</v>
+        <v>700272</v>
       </c>
       <c r="R123" t="n">
-        <v>7283816</v>
+        <v>7283984</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14113,10 +14113,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119669143</v>
+        <v>119670886</v>
       </c>
       <c r="B124" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14125,25 +14125,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14160,10 +14160,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>700542</v>
+        <v>700264</v>
       </c>
       <c r="R124" t="n">
-        <v>7283681</v>
+        <v>7283999</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14223,10 +14223,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119670746</v>
+        <v>119671053</v>
       </c>
       <c r="B125" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14235,25 +14235,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14273,7 +14273,7 @@
         <v>700272</v>
       </c>
       <c r="R125" t="n">
-        <v>7283984</v>
+        <v>7284020</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14333,10 +14333,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119670886</v>
+        <v>119670144</v>
       </c>
       <c r="B126" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14349,21 +14349,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14380,10 +14380,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>700264</v>
+        <v>700448</v>
       </c>
       <c r="R126" t="n">
-        <v>7283999</v>
+        <v>7283840</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14443,10 +14443,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119671053</v>
+        <v>119670580</v>
       </c>
       <c r="B127" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14455,25 +14455,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14490,10 +14490,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>700272</v>
+        <v>700268</v>
       </c>
       <c r="R127" t="n">
-        <v>7284020</v>
+        <v>7283948</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -1894,10 +1894,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119670119</v>
+        <v>119668598</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700452</v>
+        <v>700468</v>
       </c>
       <c r="R13" t="n">
-        <v>7283825</v>
+        <v>7283473</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119671104</v>
+        <v>119669399</v>
       </c>
       <c r="B14" t="n">
-        <v>91832</v>
+        <v>91883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2020,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700299</v>
+        <v>700529</v>
       </c>
       <c r="R14" t="n">
-        <v>7284034</v>
+        <v>7283801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119670540</v>
+        <v>119670119</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,21 +2130,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700270</v>
+        <v>700452</v>
       </c>
       <c r="R15" t="n">
-        <v>7283931</v>
+        <v>7283825</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119668598</v>
+        <v>119671104</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700468</v>
+        <v>700299</v>
       </c>
       <c r="R16" t="n">
-        <v>7283473</v>
+        <v>7284034</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,10 +2334,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119669399</v>
+        <v>119670540</v>
       </c>
       <c r="B17" t="n">
-        <v>91883</v>
+        <v>91832</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2350,21 +2350,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700529</v>
+        <v>700270</v>
       </c>
       <c r="R17" t="n">
-        <v>7283801</v>
+        <v>7283931</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119670865</v>
+        <v>119668092</v>
       </c>
       <c r="B4" t="n">
         <v>89633</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700262</v>
+        <v>700436</v>
       </c>
       <c r="R4" t="n">
-        <v>7284000</v>
+        <v>7283456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119669149</v>
+        <v>119669337</v>
       </c>
       <c r="B5" t="n">
-        <v>89633</v>
+        <v>92030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700549</v>
+        <v>700544</v>
       </c>
       <c r="R5" t="n">
-        <v>7283677</v>
+        <v>7283794</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119669271</v>
+        <v>119668875</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1127,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700583</v>
+        <v>700491</v>
       </c>
       <c r="R6" t="n">
-        <v>7283727</v>
+        <v>7283580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119668966</v>
+        <v>119669430</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,32 +1237,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1276,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700497</v>
+        <v>700515</v>
       </c>
       <c r="R7" t="n">
-        <v>7283615</v>
+        <v>7283808</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119671451</v>
+        <v>119670998</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1386,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700295</v>
+        <v>700286</v>
       </c>
       <c r="R8" t="n">
-        <v>7283983</v>
+        <v>7283999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119670372</v>
+        <v>119668514</v>
       </c>
       <c r="B9" t="n">
-        <v>91883</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,21 +1461,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1496,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700297</v>
+        <v>700458</v>
       </c>
       <c r="R9" t="n">
-        <v>7283911</v>
+        <v>7283459</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,11 +1528,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>under gammal tallåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119670470</v>
+        <v>119668715</v>
       </c>
       <c r="B10" t="n">
         <v>91840</v>
@@ -1611,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700275</v>
+        <v>700480</v>
       </c>
       <c r="R10" t="n">
-        <v>7283925</v>
+        <v>7283480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119670567</v>
+        <v>119670458</v>
       </c>
       <c r="B11" t="n">
         <v>91840</v>
@@ -1721,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700267</v>
+        <v>700272</v>
       </c>
       <c r="R11" t="n">
-        <v>7283939</v>
+        <v>7283921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119669066</v>
+        <v>119669271</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,25 +1787,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1831,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700525</v>
+        <v>700583</v>
       </c>
       <c r="R12" t="n">
-        <v>7283654</v>
+        <v>7283727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119668598</v>
+        <v>119670144</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>89633</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,21 +1901,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700468</v>
+        <v>700448</v>
       </c>
       <c r="R13" t="n">
-        <v>7283473</v>
+        <v>7283840</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119669399</v>
+        <v>119670596</v>
       </c>
       <c r="B14" t="n">
-        <v>91883</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,21 +2011,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2051,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700529</v>
+        <v>700268</v>
       </c>
       <c r="R14" t="n">
-        <v>7283801</v>
+        <v>7283952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119670119</v>
+        <v>119670353</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,25 +2117,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700452</v>
+        <v>700315</v>
       </c>
       <c r="R15" t="n">
-        <v>7283825</v>
+        <v>7283907</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,10 +2215,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119671104</v>
+        <v>119669590</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,25 +2227,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2262,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700299</v>
+        <v>700511</v>
       </c>
       <c r="R16" t="n">
-        <v>7284034</v>
+        <v>7283834</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119670540</v>
+        <v>119671069</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,25 +2337,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2381,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700270</v>
+        <v>700296</v>
       </c>
       <c r="R17" t="n">
-        <v>7283931</v>
+        <v>7284015</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2435,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119670998</v>
+        <v>119668966</v>
       </c>
       <c r="B18" t="n">
         <v>91832</v>
@@ -2477,7 +2468,11 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2491,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700286</v>
+        <v>700497</v>
       </c>
       <c r="R18" t="n">
-        <v>7283999</v>
+        <v>7283615</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,7 +2549,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119668834</v>
+        <v>119670490</v>
       </c>
       <c r="B19" t="n">
         <v>91832</v>
@@ -2601,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700478</v>
+        <v>700275</v>
       </c>
       <c r="R19" t="n">
-        <v>7283522</v>
+        <v>7283925</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2664,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119669058</v>
+        <v>119669370</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2676,25 +2671,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2706,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700528</v>
+        <v>700533</v>
       </c>
       <c r="R20" t="n">
-        <v>7283648</v>
+        <v>7283795</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119668075</v>
+        <v>119669073</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,25 +2781,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2821,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700436</v>
+        <v>700531</v>
       </c>
       <c r="R21" t="n">
-        <v>7283449</v>
+        <v>7283655</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2884,10 +2879,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119669688</v>
+        <v>119669149</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2896,25 +2891,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2931,10 +2926,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700487</v>
+        <v>700549</v>
       </c>
       <c r="R22" t="n">
-        <v>7283810</v>
+        <v>7283677</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119669503</v>
+        <v>119670346</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3010,21 +3005,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3041,10 +3036,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700527</v>
+        <v>700323</v>
       </c>
       <c r="R23" t="n">
-        <v>7283820</v>
+        <v>7283904</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3104,10 +3099,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119671583</v>
+        <v>119670283</v>
       </c>
       <c r="B24" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3116,25 +3111,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3151,10 +3146,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700309</v>
+        <v>700326</v>
       </c>
       <c r="R24" t="n">
-        <v>7283778</v>
+        <v>7283891</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3214,7 +3209,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119670353</v>
+        <v>119671624</v>
       </c>
       <c r="B25" t="n">
         <v>91840</v>
@@ -3261,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700315</v>
+        <v>700323</v>
       </c>
       <c r="R25" t="n">
-        <v>7283907</v>
+        <v>7283739</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3324,10 +3319,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119669515</v>
+        <v>119671053</v>
       </c>
       <c r="B26" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3371,10 +3366,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700532</v>
+        <v>700272</v>
       </c>
       <c r="R26" t="n">
-        <v>7283821</v>
+        <v>7284020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3429,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119670163</v>
+        <v>119670119</v>
       </c>
       <c r="B27" t="n">
         <v>91834</v>
@@ -3481,10 +3476,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700444</v>
+        <v>700452</v>
       </c>
       <c r="R27" t="n">
-        <v>7283880</v>
+        <v>7283825</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3544,7 +3539,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119670984</v>
+        <v>119669350</v>
       </c>
       <c r="B28" t="n">
         <v>91832</v>
@@ -3591,10 +3586,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700278</v>
+        <v>700547</v>
       </c>
       <c r="R28" t="n">
-        <v>7283995</v>
+        <v>7283799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3654,10 +3649,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119671635</v>
+        <v>119670470</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3670,21 +3665,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3701,10 +3696,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700317</v>
+        <v>700275</v>
       </c>
       <c r="R29" t="n">
-        <v>7283727</v>
+        <v>7283925</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3764,10 +3759,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119669445</v>
+        <v>119669524</v>
       </c>
       <c r="B30" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3776,25 +3771,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3811,10 +3806,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700524</v>
+        <v>700534</v>
       </c>
       <c r="R30" t="n">
-        <v>7283812</v>
+        <v>7283826</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3874,10 +3869,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119671463</v>
+        <v>119671393</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3886,25 +3881,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3916,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700292</v>
+        <v>700329</v>
       </c>
       <c r="R31" t="n">
-        <v>7283983</v>
+        <v>7284010</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3984,10 +3979,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119670237</v>
+        <v>119668075</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3996,25 +3991,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4031,10 +4026,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700384</v>
+        <v>700436</v>
       </c>
       <c r="R32" t="n">
-        <v>7283876</v>
+        <v>7283449</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4094,7 +4089,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119669309</v>
+        <v>119668856</v>
       </c>
       <c r="B33" t="n">
         <v>91834</v>
@@ -4141,10 +4136,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700595</v>
+        <v>700493</v>
       </c>
       <c r="R33" t="n">
-        <v>7283758</v>
+        <v>7283574</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4204,10 +4199,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119670358</v>
+        <v>119669380</v>
       </c>
       <c r="B34" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4216,25 +4211,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4251,10 +4246,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700315</v>
+        <v>700532</v>
       </c>
       <c r="R34" t="n">
-        <v>7283907</v>
+        <v>7283795</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4314,7 +4309,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119670670</v>
+        <v>119669066</v>
       </c>
       <c r="B35" t="n">
         <v>91840</v>
@@ -4361,10 +4356,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700264</v>
+        <v>700525</v>
       </c>
       <c r="R35" t="n">
-        <v>7283977</v>
+        <v>7283654</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4424,10 +4419,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119670168</v>
+        <v>119670333</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4436,25 +4431,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4471,10 +4466,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700434</v>
+        <v>700318</v>
       </c>
       <c r="R36" t="n">
-        <v>7283885</v>
+        <v>7283895</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4534,10 +4529,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119670114</v>
+        <v>119670851</v>
       </c>
       <c r="B37" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4550,21 +4545,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,10 +4576,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700457</v>
+        <v>700262</v>
       </c>
       <c r="R37" t="n">
-        <v>7283824</v>
+        <v>7283995</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4644,10 +4639,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119669670</v>
+        <v>119669112</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4656,25 +4651,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4691,10 +4686,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700494</v>
+        <v>700539</v>
       </c>
       <c r="R38" t="n">
-        <v>7283824</v>
+        <v>7283665</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4754,10 +4749,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119668809</v>
+        <v>119668747</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4766,25 +4761,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4801,10 +4796,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700481</v>
+        <v>700491</v>
       </c>
       <c r="R39" t="n">
-        <v>7283509</v>
+        <v>7283496</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4864,10 +4859,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119669590</v>
+        <v>119671463</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4876,25 +4871,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4911,10 +4906,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700511</v>
+        <v>700292</v>
       </c>
       <c r="R40" t="n">
-        <v>7283834</v>
+        <v>7283983</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4974,10 +4969,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119669114</v>
+        <v>119670645</v>
       </c>
       <c r="B41" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4986,25 +4981,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5021,10 +5016,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700530</v>
+        <v>700279</v>
       </c>
       <c r="R41" t="n">
-        <v>7283670</v>
+        <v>7283952</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5084,10 +5079,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119669250</v>
+        <v>119668829</v>
       </c>
       <c r="B42" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5100,21 +5095,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5131,10 +5126,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700565</v>
+        <v>700478</v>
       </c>
       <c r="R42" t="n">
-        <v>7283709</v>
+        <v>7283522</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5194,10 +5189,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119668910</v>
+        <v>119669670</v>
       </c>
       <c r="B43" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5206,25 +5201,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5241,10 +5236,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700502</v>
+        <v>700494</v>
       </c>
       <c r="R43" t="n">
-        <v>7283590</v>
+        <v>7283824</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5304,10 +5299,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119668926</v>
+        <v>119669063</v>
       </c>
       <c r="B44" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5316,25 +5311,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5351,10 +5346,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700502</v>
+        <v>700527</v>
       </c>
       <c r="R44" t="n">
-        <v>7283590</v>
+        <v>7283650</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5414,10 +5409,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119668423</v>
+        <v>119671431</v>
       </c>
       <c r="B45" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5426,25 +5421,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5461,10 +5456,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>700431</v>
+        <v>700310</v>
       </c>
       <c r="R45" t="n">
-        <v>7283462</v>
+        <v>7283984</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5524,10 +5519,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119670767</v>
+        <v>119669503</v>
       </c>
       <c r="B46" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5536,25 +5531,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5571,10 +5566,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700279</v>
+        <v>700527</v>
       </c>
       <c r="R46" t="n">
-        <v>7283983</v>
+        <v>7283820</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5634,10 +5629,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119671571</v>
+        <v>119668598</v>
       </c>
       <c r="B47" t="n">
-        <v>89633</v>
+        <v>91856</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5650,21 +5645,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5681,10 +5676,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700318</v>
+        <v>700468</v>
       </c>
       <c r="R47" t="n">
-        <v>7283782</v>
+        <v>7283473</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5744,10 +5739,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119668797</v>
+        <v>119670129</v>
       </c>
       <c r="B48" t="n">
-        <v>91883</v>
+        <v>91832</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5760,21 +5755,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5791,10 +5786,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700473</v>
+        <v>700456</v>
       </c>
       <c r="R48" t="n">
-        <v>7283509</v>
+        <v>7283838</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5827,11 +5822,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Under gammal tallåga!</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5859,10 +5849,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119670794</v>
+        <v>119669445</v>
       </c>
       <c r="B49" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5875,21 +5865,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5906,10 +5896,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700259</v>
+        <v>700524</v>
       </c>
       <c r="R49" t="n">
-        <v>7283993</v>
+        <v>7283812</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6079,10 +6069,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119669071</v>
+        <v>119669106</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6091,25 +6081,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6126,10 +6116,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700531</v>
+        <v>700538</v>
       </c>
       <c r="R51" t="n">
-        <v>7283655</v>
+        <v>7283663</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6189,10 +6179,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119670283</v>
+        <v>119670984</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6201,25 +6191,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6236,10 +6226,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700326</v>
+        <v>700278</v>
       </c>
       <c r="R52" t="n">
-        <v>7283891</v>
+        <v>7283995</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6299,10 +6289,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119671624</v>
+        <v>119670580</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6311,25 +6301,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6346,10 +6336,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700323</v>
+        <v>700268</v>
       </c>
       <c r="R53" t="n">
-        <v>7283739</v>
+        <v>7283948</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6409,10 +6399,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119669524</v>
+        <v>119671007</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6421,25 +6411,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6456,10 +6446,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700534</v>
+        <v>700286</v>
       </c>
       <c r="R54" t="n">
-        <v>7283826</v>
+        <v>7284004</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6519,7 +6509,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119668856</v>
+        <v>119670207</v>
       </c>
       <c r="B55" t="n">
         <v>91834</v>
@@ -6566,10 +6556,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700493</v>
+        <v>700444</v>
       </c>
       <c r="R55" t="n">
-        <v>7283574</v>
+        <v>7283897</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6629,10 +6619,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119671138</v>
+        <v>119670911</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6641,25 +6631,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6676,10 +6666,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700311</v>
+        <v>700271</v>
       </c>
       <c r="R56" t="n">
-        <v>7284032</v>
+        <v>7283996</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6739,10 +6729,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119668736</v>
+        <v>119671646</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6751,25 +6741,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6786,10 +6776,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700474</v>
+        <v>700327</v>
       </c>
       <c r="R57" t="n">
-        <v>7283486</v>
+        <v>7283730</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6849,10 +6839,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119670490</v>
+        <v>119670970</v>
       </c>
       <c r="B58" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6861,25 +6851,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6896,10 +6886,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700275</v>
+        <v>700273</v>
       </c>
       <c r="R58" t="n">
-        <v>7283925</v>
+        <v>7283993</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6959,10 +6949,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119671327</v>
+        <v>119670438</v>
       </c>
       <c r="B59" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6971,25 +6961,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7006,10 +6996,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700332</v>
+        <v>700274</v>
       </c>
       <c r="R59" t="n">
-        <v>7284034</v>
+        <v>7283915</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7069,10 +7059,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119670153</v>
+        <v>119669071</v>
       </c>
       <c r="B60" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7081,25 +7071,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7116,10 +7106,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700453</v>
+        <v>700531</v>
       </c>
       <c r="R60" t="n">
-        <v>7283845</v>
+        <v>7283655</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7179,10 +7169,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119669392</v>
+        <v>119668503</v>
       </c>
       <c r="B61" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7191,25 +7181,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7226,10 +7216,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700529</v>
+        <v>700436</v>
       </c>
       <c r="R61" t="n">
-        <v>7283801</v>
+        <v>7283469</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7289,7 +7279,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119668849</v>
+        <v>119668573</v>
       </c>
       <c r="B62" t="n">
         <v>91840</v>
@@ -7336,10 +7326,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700480</v>
+        <v>700462</v>
       </c>
       <c r="R62" t="n">
-        <v>7283558</v>
+        <v>7283460</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7399,7 +7389,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119670659</v>
+        <v>119670785</v>
       </c>
       <c r="B63" t="n">
         <v>91840</v>
@@ -7446,10 +7436,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700260</v>
+        <v>700256</v>
       </c>
       <c r="R63" t="n">
-        <v>7283959</v>
+        <v>7283992</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7509,7 +7499,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119668747</v>
+        <v>119670237</v>
       </c>
       <c r="B64" t="n">
         <v>91834</v>
@@ -7556,10 +7546,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700491</v>
+        <v>700384</v>
       </c>
       <c r="R64" t="n">
-        <v>7283496</v>
+        <v>7283876</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7619,10 +7609,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119668728</v>
+        <v>119669038</v>
       </c>
       <c r="B65" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7631,25 +7621,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7666,10 +7656,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700480</v>
+        <v>700479</v>
       </c>
       <c r="R65" t="n">
-        <v>7283482</v>
+        <v>7283639</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7729,7 +7719,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119671597</v>
+        <v>119670195</v>
       </c>
       <c r="B66" t="n">
         <v>91834</v>
@@ -7776,10 +7766,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700315</v>
+        <v>700444</v>
       </c>
       <c r="R66" t="n">
-        <v>7283776</v>
+        <v>7283887</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7839,10 +7829,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119671007</v>
+        <v>119669147</v>
       </c>
       <c r="B67" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7855,21 +7845,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7886,10 +7876,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700286</v>
+        <v>700546</v>
       </c>
       <c r="R67" t="n">
-        <v>7284004</v>
+        <v>7283682</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7949,10 +7939,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119668636</v>
+        <v>119671088</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7961,32 +7951,28 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -8000,10 +7986,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700481</v>
+        <v>700306</v>
       </c>
       <c r="R68" t="n">
-        <v>7283469</v>
+        <v>7283997</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8063,10 +8049,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119670230</v>
+        <v>119671104</v>
       </c>
       <c r="B69" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8075,25 +8061,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8110,10 +8096,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700384</v>
+        <v>700299</v>
       </c>
       <c r="R69" t="n">
-        <v>7283876</v>
+        <v>7284034</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8173,10 +8159,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119669112</v>
+        <v>119671327</v>
       </c>
       <c r="B70" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8189,21 +8175,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8220,10 +8206,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700539</v>
+        <v>700332</v>
       </c>
       <c r="R70" t="n">
-        <v>7283665</v>
+        <v>7284034</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8283,10 +8269,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119669042</v>
+        <v>119670717</v>
       </c>
       <c r="B71" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8295,25 +8281,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8330,10 +8316,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700479</v>
+        <v>700303</v>
       </c>
       <c r="R71" t="n">
-        <v>7283639</v>
+        <v>7283965</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8393,7 +8379,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119668503</v>
+        <v>119671159</v>
       </c>
       <c r="B72" t="n">
         <v>91840</v>
@@ -8440,10 +8426,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700436</v>
+        <v>700313</v>
       </c>
       <c r="R72" t="n">
-        <v>7283469</v>
+        <v>7284032</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8503,10 +8489,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119669410</v>
+        <v>119671583</v>
       </c>
       <c r="B73" t="n">
-        <v>91834</v>
+        <v>90807</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8515,25 +8501,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8550,10 +8536,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700511</v>
+        <v>700309</v>
       </c>
       <c r="R73" t="n">
-        <v>7283802</v>
+        <v>7283778</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8613,10 +8599,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119668593</v>
+        <v>119669004</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8629,21 +8615,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8660,10 +8646,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700468</v>
+        <v>700498</v>
       </c>
       <c r="R74" t="n">
-        <v>7283473</v>
+        <v>7283624</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8833,10 +8819,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119668841</v>
+        <v>119670220</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8849,21 +8835,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8880,10 +8866,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700476</v>
+        <v>700396</v>
       </c>
       <c r="R76" t="n">
-        <v>7283544</v>
+        <v>7283874</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8943,7 +8929,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119670717</v>
+        <v>119671043</v>
       </c>
       <c r="B77" t="n">
         <v>91840</v>
@@ -8990,10 +8976,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700303</v>
+        <v>700268</v>
       </c>
       <c r="R77" t="n">
-        <v>7283965</v>
+        <v>7284015</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9053,10 +9039,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119669620</v>
+        <v>119669399</v>
       </c>
       <c r="B78" t="n">
-        <v>91852</v>
+        <v>91883</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9065,25 +9051,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9100,10 +9086,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700508</v>
+        <v>700529</v>
       </c>
       <c r="R78" t="n">
-        <v>7283824</v>
+        <v>7283801</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9163,10 +9149,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119670301</v>
+        <v>119669419</v>
       </c>
       <c r="B79" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9175,25 +9161,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9210,10 +9196,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700314</v>
+        <v>700519</v>
       </c>
       <c r="R79" t="n">
-        <v>7283890</v>
+        <v>7283805</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9273,10 +9259,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119669419</v>
+        <v>119668760</v>
       </c>
       <c r="B80" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9285,25 +9271,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9320,10 +9306,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700519</v>
+        <v>700485</v>
       </c>
       <c r="R80" t="n">
-        <v>7283805</v>
+        <v>7283507</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9383,10 +9369,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119669073</v>
+        <v>119669592</v>
       </c>
       <c r="B81" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9395,25 +9381,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9430,10 +9416,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700531</v>
+        <v>700511</v>
       </c>
       <c r="R81" t="n">
-        <v>7283655</v>
+        <v>7283834</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9493,10 +9479,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119671646</v>
+        <v>119670567</v>
       </c>
       <c r="B82" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9505,25 +9491,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9540,10 +9526,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700327</v>
+        <v>700267</v>
       </c>
       <c r="R82" t="n">
-        <v>7283730</v>
+        <v>7283939</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9603,7 +9589,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119668690</v>
+        <v>119669138</v>
       </c>
       <c r="B83" t="n">
         <v>91840</v>
@@ -9650,10 +9636,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700485</v>
+        <v>700540</v>
       </c>
       <c r="R83" t="n">
-        <v>7283480</v>
+        <v>7283677</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9713,10 +9699,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119670851</v>
+        <v>119671571</v>
       </c>
       <c r="B84" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9729,21 +9715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9760,10 +9746,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700262</v>
+        <v>700318</v>
       </c>
       <c r="R84" t="n">
-        <v>7283995</v>
+        <v>7283782</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9823,10 +9809,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119670220</v>
+        <v>119670163</v>
       </c>
       <c r="B85" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9835,25 +9821,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9870,10 +9856,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>700396</v>
+        <v>700444</v>
       </c>
       <c r="R85" t="n">
-        <v>7283874</v>
+        <v>7283880</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9933,10 +9919,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119669038</v>
+        <v>119669114</v>
       </c>
       <c r="B86" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9945,25 +9931,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9980,10 +9966,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>700479</v>
+        <v>700530</v>
       </c>
       <c r="R86" t="n">
-        <v>7283639</v>
+        <v>7283670</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10043,7 +10029,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119669138</v>
+        <v>119669058</v>
       </c>
       <c r="B87" t="n">
         <v>91840</v>
@@ -10090,10 +10076,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700540</v>
+        <v>700528</v>
       </c>
       <c r="R87" t="n">
-        <v>7283677</v>
+        <v>7283648</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10153,10 +10139,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119670959</v>
+        <v>119669297</v>
       </c>
       <c r="B88" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10165,25 +10151,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10200,10 +10186,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700274</v>
+        <v>700594</v>
       </c>
       <c r="R88" t="n">
-        <v>7283995</v>
+        <v>7283740</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10263,10 +10249,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119670195</v>
+        <v>119671635</v>
       </c>
       <c r="B89" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10275,25 +10261,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10310,10 +10296,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>700444</v>
+        <v>700317</v>
       </c>
       <c r="R89" t="n">
-        <v>7283887</v>
+        <v>7283727</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10373,7 +10359,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119669380</v>
+        <v>119668841</v>
       </c>
       <c r="B90" t="n">
         <v>91840</v>
@@ -10420,10 +10406,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>700532</v>
+        <v>700476</v>
       </c>
       <c r="R90" t="n">
-        <v>7283795</v>
+        <v>7283544</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10483,7 +10469,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119671159</v>
+        <v>119671608</v>
       </c>
       <c r="B91" t="n">
         <v>91840</v>
@@ -10530,10 +10516,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>700313</v>
+        <v>700327</v>
       </c>
       <c r="R91" t="n">
-        <v>7284032</v>
+        <v>7283760</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10593,10 +10579,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119669147</v>
+        <v>119670670</v>
       </c>
       <c r="B92" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10605,25 +10591,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10640,10 +10626,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>700546</v>
+        <v>700264</v>
       </c>
       <c r="R92" t="n">
-        <v>7283682</v>
+        <v>7283977</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10703,7 +10689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119671608</v>
+        <v>119671138</v>
       </c>
       <c r="B93" t="n">
         <v>91840</v>
@@ -10750,10 +10736,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700327</v>
+        <v>700311</v>
       </c>
       <c r="R93" t="n">
-        <v>7283760</v>
+        <v>7284032</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10813,10 +10799,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119670129</v>
+        <v>119668910</v>
       </c>
       <c r="B94" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10829,21 +10815,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10860,10 +10846,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>700456</v>
+        <v>700502</v>
       </c>
       <c r="R94" t="n">
-        <v>7283838</v>
+        <v>7283590</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10923,10 +10909,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119670438</v>
+        <v>119671451</v>
       </c>
       <c r="B95" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10935,25 +10921,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10970,10 +10956,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>700274</v>
+        <v>700295</v>
       </c>
       <c r="R95" t="n">
-        <v>7283915</v>
+        <v>7283983</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11033,10 +11019,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119670346</v>
+        <v>119670865</v>
       </c>
       <c r="B96" t="n">
-        <v>91852</v>
+        <v>89633</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11045,25 +11031,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11080,10 +11066,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>700323</v>
+        <v>700262</v>
       </c>
       <c r="R96" t="n">
-        <v>7283904</v>
+        <v>7284000</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11143,10 +11129,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119671393</v>
+        <v>119670801</v>
       </c>
       <c r="B97" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11155,25 +11141,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11190,10 +11176,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>700329</v>
+        <v>700262</v>
       </c>
       <c r="R97" t="n">
-        <v>7284010</v>
+        <v>7283995</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11253,7 +11239,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119670785</v>
+        <v>119669683</v>
       </c>
       <c r="B98" t="n">
         <v>91840</v>
@@ -11300,10 +11286,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>700256</v>
+        <v>700488</v>
       </c>
       <c r="R98" t="n">
-        <v>7283992</v>
+        <v>7283816</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11363,10 +11349,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119670941</v>
+        <v>119668849</v>
       </c>
       <c r="B99" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11375,25 +11361,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11410,10 +11396,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>700274</v>
+        <v>700480</v>
       </c>
       <c r="R99" t="n">
-        <v>7283997</v>
+        <v>7283558</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11473,10 +11459,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119669674</v>
+        <v>119669620</v>
       </c>
       <c r="B100" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11485,25 +11471,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11520,7 +11506,7 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>700494</v>
+        <v>700508</v>
       </c>
       <c r="R100" t="n">
         <v>7283824</v>
@@ -11583,10 +11569,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119668709</v>
+        <v>119668736</v>
       </c>
       <c r="B101" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11595,25 +11581,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11630,10 +11616,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>700480</v>
+        <v>700474</v>
       </c>
       <c r="R101" t="n">
-        <v>7283480</v>
+        <v>7283486</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11693,10 +11679,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119670970</v>
+        <v>119671117</v>
       </c>
       <c r="B102" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11705,25 +11691,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11740,10 +11726,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>700273</v>
+        <v>700298</v>
       </c>
       <c r="R102" t="n">
-        <v>7283993</v>
+        <v>7284037</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11803,10 +11789,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119671088</v>
+        <v>119669042</v>
       </c>
       <c r="B103" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11819,21 +11805,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11850,10 +11836,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>700306</v>
+        <v>700479</v>
       </c>
       <c r="R103" t="n">
-        <v>7283997</v>
+        <v>7283639</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11913,10 +11899,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119671618</v>
+        <v>119668728</v>
       </c>
       <c r="B104" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11925,25 +11911,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11960,10 +11946,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>700324</v>
+        <v>700480</v>
       </c>
       <c r="R104" t="n">
-        <v>7283744</v>
+        <v>7283482</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12023,7 +12009,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119669063</v>
+        <v>119671618</v>
       </c>
       <c r="B105" t="n">
         <v>91840</v>
@@ -12070,10 +12056,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>700527</v>
+        <v>700324</v>
       </c>
       <c r="R105" t="n">
-        <v>7283650</v>
+        <v>7283744</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12133,10 +12119,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119669430</v>
+        <v>119670256</v>
       </c>
       <c r="B106" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12149,21 +12135,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12180,10 +12166,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>700515</v>
+        <v>700334</v>
       </c>
       <c r="R106" t="n">
-        <v>7283808</v>
+        <v>7283862</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12243,10 +12229,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119671431</v>
+        <v>119670259</v>
       </c>
       <c r="B107" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12259,21 +12245,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12290,10 +12276,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>700310</v>
+        <v>700337</v>
       </c>
       <c r="R107" t="n">
-        <v>7283984</v>
+        <v>7283884</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12353,10 +12339,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119670106</v>
+        <v>119670301</v>
       </c>
       <c r="B108" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12365,25 +12351,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12400,10 +12386,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>700463</v>
+        <v>700314</v>
       </c>
       <c r="R108" t="n">
-        <v>7283819</v>
+        <v>7283890</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12463,10 +12449,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119669103</v>
+        <v>119669392</v>
       </c>
       <c r="B109" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12475,25 +12461,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12510,10 +12496,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>700544</v>
+        <v>700529</v>
       </c>
       <c r="R109" t="n">
-        <v>7283659</v>
+        <v>7283801</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12573,10 +12559,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119668514</v>
+        <v>119670746</v>
       </c>
       <c r="B110" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12589,21 +12575,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12620,10 +12606,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>700458</v>
+        <v>700272</v>
       </c>
       <c r="R110" t="n">
-        <v>7283459</v>
+        <v>7283984</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12683,10 +12669,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119670801</v>
+        <v>119670106</v>
       </c>
       <c r="B111" t="n">
-        <v>91844</v>
+        <v>91832</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12695,25 +12681,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12730,10 +12716,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>700262</v>
+        <v>700463</v>
       </c>
       <c r="R111" t="n">
-        <v>7283995</v>
+        <v>7283819</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12793,7 +12779,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119668875</v>
+        <v>119670168</v>
       </c>
       <c r="B112" t="n">
         <v>91840</v>
@@ -12840,10 +12826,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>700491</v>
+        <v>700434</v>
       </c>
       <c r="R112" t="n">
-        <v>7283580</v>
+        <v>7283885</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12903,10 +12889,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119668829</v>
+        <v>119669515</v>
       </c>
       <c r="B113" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12919,21 +12905,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12950,10 +12936,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>700478</v>
+        <v>700532</v>
       </c>
       <c r="R113" t="n">
-        <v>7283522</v>
+        <v>7283821</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13013,7 +12999,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119669297</v>
+        <v>119668809</v>
       </c>
       <c r="B114" t="n">
         <v>91840</v>
@@ -13060,10 +13046,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>700594</v>
+        <v>700481</v>
       </c>
       <c r="R114" t="n">
-        <v>7283740</v>
+        <v>7283509</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13123,10 +13109,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119670207</v>
+        <v>119668636</v>
       </c>
       <c r="B115" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13135,28 +13121,32 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -13170,10 +13160,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>700444</v>
+        <v>700481</v>
       </c>
       <c r="R115" t="n">
-        <v>7283897</v>
+        <v>7283469</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13233,7 +13223,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119670911</v>
+        <v>119670540</v>
       </c>
       <c r="B116" t="n">
         <v>91832</v>
@@ -13280,10 +13270,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>700271</v>
+        <v>700270</v>
       </c>
       <c r="R116" t="n">
-        <v>7283996</v>
+        <v>7283931</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13343,10 +13333,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119671069</v>
+        <v>119669309</v>
       </c>
       <c r="B117" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13355,25 +13345,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13390,10 +13380,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>700296</v>
+        <v>700595</v>
       </c>
       <c r="R117" t="n">
-        <v>7284015</v>
+        <v>7283758</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13453,10 +13443,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119668945</v>
+        <v>119670777</v>
       </c>
       <c r="B118" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13465,25 +13455,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13500,10 +13490,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>700493</v>
+        <v>700279</v>
       </c>
       <c r="R118" t="n">
-        <v>7283596</v>
+        <v>7283988</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13563,10 +13553,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119668715</v>
+        <v>119669674</v>
       </c>
       <c r="B119" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13575,25 +13565,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13610,10 +13600,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>700480</v>
+        <v>700494</v>
       </c>
       <c r="R119" t="n">
-        <v>7283480</v>
+        <v>7283824</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13673,10 +13663,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119670645</v>
+        <v>119668701</v>
       </c>
       <c r="B120" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13685,25 +13675,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13720,10 +13710,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>700279</v>
+        <v>700485</v>
       </c>
       <c r="R120" t="n">
-        <v>7283952</v>
+        <v>7283480</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13783,10 +13773,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119669683</v>
+        <v>119668709</v>
       </c>
       <c r="B121" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13795,25 +13785,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13830,10 +13820,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>700488</v>
+        <v>700480</v>
       </c>
       <c r="R121" t="n">
-        <v>7283816</v>
+        <v>7283480</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13893,7 +13883,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119669143</v>
+        <v>119669103</v>
       </c>
       <c r="B122" t="n">
         <v>91840</v>
@@ -13940,10 +13930,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>700542</v>
+        <v>700544</v>
       </c>
       <c r="R122" t="n">
-        <v>7283681</v>
+        <v>7283659</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14003,10 +13993,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119670746</v>
+        <v>119668690</v>
       </c>
       <c r="B123" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14015,25 +14005,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14050,10 +14040,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>700272</v>
+        <v>700485</v>
       </c>
       <c r="R123" t="n">
-        <v>7283984</v>
+        <v>7283480</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14113,10 +14103,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119670886</v>
+        <v>119670659</v>
       </c>
       <c r="B124" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14125,25 +14115,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14160,10 +14150,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>700264</v>
+        <v>700260</v>
       </c>
       <c r="R124" t="n">
-        <v>7283999</v>
+        <v>7283959</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14223,10 +14213,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119671053</v>
+        <v>119669634</v>
       </c>
       <c r="B125" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14239,21 +14229,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14270,10 +14260,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>700272</v>
+        <v>700503</v>
       </c>
       <c r="R125" t="n">
-        <v>7284020</v>
+        <v>7283829</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14333,10 +14323,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119670144</v>
+        <v>119669000</v>
       </c>
       <c r="B126" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14345,25 +14335,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14380,10 +14370,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>700448</v>
+        <v>700509</v>
       </c>
       <c r="R126" t="n">
-        <v>7283840</v>
+        <v>7283621</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14443,10 +14433,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119670580</v>
+        <v>119670114</v>
       </c>
       <c r="B127" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14459,21 +14449,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14490,10 +14480,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>700268</v>
+        <v>700457</v>
       </c>
       <c r="R127" t="n">
-        <v>7283948</v>
+        <v>7283824</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14553,7 +14543,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119669471</v>
+        <v>119669320</v>
       </c>
       <c r="B128" t="n">
         <v>91852</v>
@@ -14600,10 +14590,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>700537</v>
+        <v>700590</v>
       </c>
       <c r="R128" t="n">
-        <v>7283817</v>
+        <v>7283790</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14663,10 +14653,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119671117</v>
+        <v>119668945</v>
       </c>
       <c r="B129" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14675,25 +14665,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14710,10 +14700,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>700298</v>
+        <v>700493</v>
       </c>
       <c r="R129" t="n">
-        <v>7284037</v>
+        <v>7283596</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14773,10 +14763,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119668760</v>
+        <v>119671597</v>
       </c>
       <c r="B130" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14785,25 +14775,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14820,10 +14810,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>700485</v>
+        <v>700315</v>
       </c>
       <c r="R130" t="n">
-        <v>7283507</v>
+        <v>7283776</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14883,10 +14873,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119669476</v>
+        <v>119668797</v>
       </c>
       <c r="B131" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14895,25 +14885,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14930,10 +14920,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>700537</v>
+        <v>700473</v>
       </c>
       <c r="R131" t="n">
-        <v>7283817</v>
+        <v>7283509</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14966,6 +14956,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Under gammal tallåga!</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14993,10 +14988,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119670596</v>
+        <v>119670372</v>
       </c>
       <c r="B132" t="n">
-        <v>91832</v>
+        <v>91883</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15009,21 +15004,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15040,10 +15035,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>700268</v>
+        <v>700297</v>
       </c>
       <c r="R132" t="n">
-        <v>7283952</v>
+        <v>7283911</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15076,6 +15071,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>under gammal tallåga</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15103,10 +15103,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119670777</v>
+        <v>119668926</v>
       </c>
       <c r="B133" t="n">
-        <v>92030</v>
+        <v>91884</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15119,21 +15119,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15150,10 +15150,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>700279</v>
+        <v>700502</v>
       </c>
       <c r="R133" t="n">
-        <v>7283988</v>
+        <v>7283590</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15213,10 +15213,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119670333</v>
+        <v>119670358</v>
       </c>
       <c r="B134" t="n">
-        <v>89633</v>
+        <v>91856</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15229,21 +15229,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15260,10 +15260,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>700318</v>
+        <v>700315</v>
       </c>
       <c r="R134" t="n">
-        <v>7283895</v>
+        <v>7283907</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15323,10 +15323,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119668701</v>
+        <v>119669471</v>
       </c>
       <c r="B135" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15335,25 +15335,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15370,10 +15370,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>700485</v>
+        <v>700537</v>
       </c>
       <c r="R135" t="n">
-        <v>7283480</v>
+        <v>7283817</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15433,10 +15433,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119670458</v>
+        <v>119670430</v>
       </c>
       <c r="B136" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15449,21 +15449,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>700272</v>
+        <v>700280</v>
       </c>
       <c r="R136" t="n">
-        <v>7283921</v>
+        <v>7283905</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15543,10 +15543,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119669592</v>
+        <v>119668834</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15555,25 +15555,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15590,10 +15590,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>700511</v>
+        <v>700478</v>
       </c>
       <c r="R137" t="n">
-        <v>7283834</v>
+        <v>7283522</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15653,10 +15653,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119669106</v>
+        <v>119670767</v>
       </c>
       <c r="B138" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15669,21 +15669,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15700,10 +15700,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>700538</v>
+        <v>700279</v>
       </c>
       <c r="R138" t="n">
-        <v>7283663</v>
+        <v>7283983</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15763,10 +15763,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119670256</v>
+        <v>119669410</v>
       </c>
       <c r="B139" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15775,25 +15775,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15810,10 +15810,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>700334</v>
+        <v>700511</v>
       </c>
       <c r="R139" t="n">
-        <v>7283862</v>
+        <v>7283802</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15873,10 +15873,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119669370</v>
+        <v>119669476</v>
       </c>
       <c r="B140" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15885,25 +15885,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15920,10 +15920,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>700533</v>
+        <v>700537</v>
       </c>
       <c r="R140" t="n">
-        <v>7283795</v>
+        <v>7283817</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15983,10 +15983,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119669350</v>
+        <v>119670772</v>
       </c>
       <c r="B141" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15995,25 +15995,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16030,10 +16030,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>700547</v>
+        <v>700279</v>
       </c>
       <c r="R141" t="n">
-        <v>7283799</v>
+        <v>7283983</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16093,10 +16093,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119668092</v>
+        <v>119669143</v>
       </c>
       <c r="B142" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16105,25 +16105,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16140,10 +16140,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>700436</v>
+        <v>700542</v>
       </c>
       <c r="R142" t="n">
-        <v>7283456</v>
+        <v>7283681</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16203,10 +16203,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119669337</v>
+        <v>119669688</v>
       </c>
       <c r="B143" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16215,25 +16215,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16250,10 +16250,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>700544</v>
+        <v>700487</v>
       </c>
       <c r="R143" t="n">
-        <v>7283794</v>
+        <v>7283810</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16313,10 +16313,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119669004</v>
+        <v>119670153</v>
       </c>
       <c r="B144" t="n">
-        <v>91852</v>
+        <v>92030</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16325,25 +16325,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4366</v>
+        <v>2079</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>700498</v>
+        <v>700453</v>
       </c>
       <c r="R144" t="n">
-        <v>7283624</v>
+        <v>7283845</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16423,10 +16423,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119670430</v>
+        <v>119670941</v>
       </c>
       <c r="B145" t="n">
-        <v>91852</v>
+        <v>89633</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16435,25 +16435,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16470,10 +16470,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>700280</v>
+        <v>700274</v>
       </c>
       <c r="R145" t="n">
-        <v>7283905</v>
+        <v>7283997</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16533,7 +16533,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119670772</v>
+        <v>119670230</v>
       </c>
       <c r="B146" t="n">
         <v>91840</v>
@@ -16580,10 +16580,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>700279</v>
+        <v>700384</v>
       </c>
       <c r="R146" t="n">
-        <v>7283983</v>
+        <v>7283876</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16643,10 +16643,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119668573</v>
+        <v>119668423</v>
       </c>
       <c r="B147" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16655,25 +16655,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16690,10 +16690,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>700462</v>
+        <v>700431</v>
       </c>
       <c r="R147" t="n">
-        <v>7283460</v>
+        <v>7283462</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16753,10 +16753,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119671043</v>
+        <v>119670794</v>
       </c>
       <c r="B148" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16765,25 +16765,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16800,10 +16800,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>700268</v>
+        <v>700259</v>
       </c>
       <c r="R148" t="n">
-        <v>7284015</v>
+        <v>7283993</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16863,10 +16863,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119669634</v>
+        <v>119668593</v>
       </c>
       <c r="B149" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16879,21 +16879,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16910,10 +16910,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>700503</v>
+        <v>700468</v>
       </c>
       <c r="R149" t="n">
-        <v>7283829</v>
+        <v>7283473</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16973,7 +16973,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119670259</v>
+        <v>119669250</v>
       </c>
       <c r="B150" t="n">
         <v>91852</v>
@@ -17020,10 +17020,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>700337</v>
+        <v>700565</v>
       </c>
       <c r="R150" t="n">
-        <v>7283884</v>
+        <v>7283709</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17083,10 +17083,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119669320</v>
+        <v>119670886</v>
       </c>
       <c r="B151" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17095,25 +17095,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17130,10 +17130,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>700590</v>
+        <v>700264</v>
       </c>
       <c r="R151" t="n">
-        <v>7283790</v>
+        <v>7283999</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17193,10 +17193,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119669000</v>
+        <v>119670959</v>
       </c>
       <c r="B152" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17205,25 +17205,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17240,10 +17240,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>700509</v>
+        <v>700274</v>
       </c>
       <c r="R152" t="n">
-        <v>7283621</v>
+        <v>7283995</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -1445,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119668514</v>
+        <v>119668715</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,25 +1457,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700458</v>
+        <v>700480</v>
       </c>
       <c r="R9" t="n">
-        <v>7283459</v>
+        <v>7283480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119668715</v>
+        <v>119670458</v>
       </c>
       <c r="B10" t="n">
         <v>91840</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700480</v>
+        <v>700272</v>
       </c>
       <c r="R10" t="n">
-        <v>7283480</v>
+        <v>7283921</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119670458</v>
+        <v>119669271</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700272</v>
+        <v>700583</v>
       </c>
       <c r="R11" t="n">
-        <v>7283921</v>
+        <v>7283727</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119669271</v>
+        <v>119668514</v>
       </c>
       <c r="B12" t="n">
         <v>91834</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700583</v>
+        <v>700458</v>
       </c>
       <c r="R12" t="n">
-        <v>7283727</v>
+        <v>7283459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119669066</v>
+        <v>119670645</v>
       </c>
       <c r="B35" t="n">
         <v>91840</v>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700525</v>
+        <v>700279</v>
       </c>
       <c r="R35" t="n">
-        <v>7283654</v>
+        <v>7283952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4639,7 +4639,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119669112</v>
+        <v>119668747</v>
       </c>
       <c r="B38" t="n">
         <v>91834</v>
@@ -4686,10 +4686,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700539</v>
+        <v>700491</v>
       </c>
       <c r="R38" t="n">
-        <v>7283665</v>
+        <v>7283496</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119668747</v>
+        <v>119671463</v>
       </c>
       <c r="B39" t="n">
         <v>91834</v>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700491</v>
+        <v>700292</v>
       </c>
       <c r="R39" t="n">
-        <v>7283496</v>
+        <v>7283983</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4859,10 +4859,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119671463</v>
+        <v>119669066</v>
       </c>
       <c r="B40" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4871,25 +4871,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700292</v>
+        <v>700525</v>
       </c>
       <c r="R40" t="n">
-        <v>7283983</v>
+        <v>7283654</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119670645</v>
+        <v>119669112</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700279</v>
+        <v>700539</v>
       </c>
       <c r="R41" t="n">
-        <v>7283952</v>
+        <v>7283665</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6289,10 +6289,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119670580</v>
+        <v>119671646</v>
       </c>
       <c r="B53" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6305,21 +6305,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700268</v>
+        <v>700327</v>
       </c>
       <c r="R53" t="n">
-        <v>7283948</v>
+        <v>7283730</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119671646</v>
+        <v>119670580</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700327</v>
+        <v>700268</v>
       </c>
       <c r="R57" t="n">
-        <v>7283730</v>
+        <v>7283948</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6839,10 +6839,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119670970</v>
+        <v>119670237</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6851,25 +6851,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700273</v>
+        <v>700384</v>
       </c>
       <c r="R58" t="n">
-        <v>7283993</v>
+        <v>7283876</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6949,7 +6949,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119670438</v>
+        <v>119670970</v>
       </c>
       <c r="B59" t="n">
         <v>91840</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700274</v>
+        <v>700273</v>
       </c>
       <c r="R59" t="n">
-        <v>7283915</v>
+        <v>7283993</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7059,7 +7059,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119669071</v>
+        <v>119670438</v>
       </c>
       <c r="B60" t="n">
         <v>91840</v>
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700531</v>
+        <v>700274</v>
       </c>
       <c r="R60" t="n">
-        <v>7283655</v>
+        <v>7283915</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7169,7 +7169,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119668503</v>
+        <v>119669071</v>
       </c>
       <c r="B61" t="n">
         <v>91840</v>
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700436</v>
+        <v>700531</v>
       </c>
       <c r="R61" t="n">
-        <v>7283469</v>
+        <v>7283655</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7279,7 +7279,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119668573</v>
+        <v>119668503</v>
       </c>
       <c r="B62" t="n">
         <v>91840</v>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700462</v>
+        <v>700436</v>
       </c>
       <c r="R62" t="n">
-        <v>7283460</v>
+        <v>7283469</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7389,7 +7389,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119670785</v>
+        <v>119668573</v>
       </c>
       <c r="B63" t="n">
         <v>91840</v>
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700256</v>
+        <v>700462</v>
       </c>
       <c r="R63" t="n">
-        <v>7283992</v>
+        <v>7283460</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7499,10 +7499,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119670237</v>
+        <v>119670785</v>
       </c>
       <c r="B64" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7511,25 +7511,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7546,10 +7546,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700384</v>
+        <v>700256</v>
       </c>
       <c r="R64" t="n">
-        <v>7283876</v>
+        <v>7283992</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8489,10 +8489,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119671583</v>
+        <v>119669004</v>
       </c>
       <c r="B73" t="n">
-        <v>90807</v>
+        <v>91852</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8501,25 +8501,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>65</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700309</v>
+        <v>700498</v>
       </c>
       <c r="R73" t="n">
-        <v>7283778</v>
+        <v>7283624</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8599,7 +8599,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119669004</v>
+        <v>119671626</v>
       </c>
       <c r="B74" t="n">
         <v>91852</v>
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700498</v>
+        <v>700323</v>
       </c>
       <c r="R74" t="n">
-        <v>7283624</v>
+        <v>7283739</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8709,7 +8709,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119671626</v>
+        <v>119670220</v>
       </c>
       <c r="B75" t="n">
         <v>91852</v>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700323</v>
+        <v>700396</v>
       </c>
       <c r="R75" t="n">
-        <v>7283739</v>
+        <v>7283874</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8819,10 +8819,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119670220</v>
+        <v>119671043</v>
       </c>
       <c r="B76" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8835,21 +8835,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8866,10 +8866,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700396</v>
+        <v>700268</v>
       </c>
       <c r="R76" t="n">
-        <v>7283874</v>
+        <v>7284015</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119671043</v>
+        <v>119669399</v>
       </c>
       <c r="B77" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8941,25 +8941,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8976,10 +8976,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700268</v>
+        <v>700529</v>
       </c>
       <c r="R77" t="n">
-        <v>7284015</v>
+        <v>7283801</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9039,10 +9039,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119669399</v>
+        <v>119669419</v>
       </c>
       <c r="B78" t="n">
-        <v>91883</v>
+        <v>91832</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9055,21 +9055,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700529</v>
+        <v>700519</v>
       </c>
       <c r="R78" t="n">
-        <v>7283801</v>
+        <v>7283805</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9149,10 +9149,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119669419</v>
+        <v>119671583</v>
       </c>
       <c r="B79" t="n">
-        <v>91832</v>
+        <v>90807</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9161,25 +9161,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4361</v>
+        <v>65</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9196,10 +9196,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700519</v>
+        <v>700309</v>
       </c>
       <c r="R79" t="n">
-        <v>7283805</v>
+        <v>7283778</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119668841</v>
+        <v>119670670</v>
       </c>
       <c r="B90" t="n">
         <v>91840</v>
@@ -10406,10 +10406,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>700476</v>
+        <v>700264</v>
       </c>
       <c r="R90" t="n">
-        <v>7283544</v>
+        <v>7283977</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10469,7 +10469,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119671608</v>
+        <v>119668841</v>
       </c>
       <c r="B91" t="n">
         <v>91840</v>
@@ -10516,10 +10516,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>700327</v>
+        <v>700476</v>
       </c>
       <c r="R91" t="n">
-        <v>7283760</v>
+        <v>7283544</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10579,7 +10579,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119670670</v>
+        <v>119671138</v>
       </c>
       <c r="B92" t="n">
         <v>91840</v>
@@ -10626,10 +10626,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>700264</v>
+        <v>700311</v>
       </c>
       <c r="R92" t="n">
-        <v>7283977</v>
+        <v>7284032</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10689,7 +10689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119671138</v>
+        <v>119671608</v>
       </c>
       <c r="B93" t="n">
         <v>91840</v>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700311</v>
+        <v>700327</v>
       </c>
       <c r="R93" t="n">
-        <v>7284032</v>
+        <v>7283760</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119668092</v>
+        <v>119671117</v>
       </c>
       <c r="B4" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700436</v>
+        <v>700298</v>
       </c>
       <c r="R4" t="n">
-        <v>7283456</v>
+        <v>7284037</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119669337</v>
+        <v>119670195</v>
       </c>
       <c r="B5" t="n">
-        <v>92030</v>
+        <v>91834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700544</v>
+        <v>700444</v>
       </c>
       <c r="R5" t="n">
-        <v>7283794</v>
+        <v>7283887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119668875</v>
+        <v>119668760</v>
       </c>
       <c r="B6" t="n">
         <v>91840</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700491</v>
+        <v>700485</v>
       </c>
       <c r="R6" t="n">
-        <v>7283580</v>
+        <v>7283507</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119669430</v>
+        <v>119669476</v>
       </c>
       <c r="B7" t="n">
         <v>91840</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700515</v>
+        <v>700537</v>
       </c>
       <c r="R7" t="n">
-        <v>7283808</v>
+        <v>7283817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119670998</v>
+        <v>119668834</v>
       </c>
       <c r="B8" t="n">
         <v>91832</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700286</v>
+        <v>700478</v>
       </c>
       <c r="R8" t="n">
-        <v>7283999</v>
+        <v>7283522</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119668715</v>
+        <v>119670353</v>
       </c>
       <c r="B9" t="n">
         <v>91840</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700480</v>
+        <v>700315</v>
       </c>
       <c r="R9" t="n">
-        <v>7283480</v>
+        <v>7283907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119670458</v>
+        <v>119670717</v>
       </c>
       <c r="B10" t="n">
         <v>91840</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700272</v>
+        <v>700303</v>
       </c>
       <c r="R10" t="n">
-        <v>7283921</v>
+        <v>7283965</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119669271</v>
+        <v>119671463</v>
       </c>
       <c r="B11" t="n">
         <v>91834</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700583</v>
+        <v>700292</v>
       </c>
       <c r="R11" t="n">
-        <v>7283727</v>
+        <v>7283983</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119668514</v>
+        <v>119670777</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>92030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,21 +1791,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700458</v>
+        <v>700279</v>
       </c>
       <c r="R12" t="n">
-        <v>7283459</v>
+        <v>7283988</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119670144</v>
+        <v>119668841</v>
       </c>
       <c r="B13" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1897,25 +1897,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700448</v>
+        <v>700476</v>
       </c>
       <c r="R13" t="n">
-        <v>7283840</v>
+        <v>7283544</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119670596</v>
+        <v>119669073</v>
       </c>
       <c r="B14" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700268</v>
+        <v>700531</v>
       </c>
       <c r="R14" t="n">
-        <v>7283952</v>
+        <v>7283655</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119670353</v>
+        <v>119669430</v>
       </c>
       <c r="B15" t="n">
         <v>91840</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700315</v>
+        <v>700515</v>
       </c>
       <c r="R15" t="n">
-        <v>7283907</v>
+        <v>7283808</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119669590</v>
+        <v>119670785</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700511</v>
+        <v>700256</v>
       </c>
       <c r="R16" t="n">
-        <v>7283834</v>
+        <v>7283992</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119671069</v>
+        <v>119670301</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700296</v>
+        <v>700314</v>
       </c>
       <c r="R17" t="n">
-        <v>7284015</v>
+        <v>7283890</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119668966</v>
+        <v>119670168</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2447,32 +2447,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2486,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700497</v>
+        <v>700434</v>
       </c>
       <c r="R18" t="n">
-        <v>7283615</v>
+        <v>7283885</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,10 +2545,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119670490</v>
+        <v>119670458</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2561,25 +2557,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2596,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700275</v>
+        <v>700272</v>
       </c>
       <c r="R19" t="n">
-        <v>7283925</v>
+        <v>7283921</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,10 +2655,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119669370</v>
+        <v>119671646</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,21 +2671,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2706,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700533</v>
+        <v>700327</v>
       </c>
       <c r="R20" t="n">
-        <v>7283795</v>
+        <v>7283730</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2769,10 +2765,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119669073</v>
+        <v>119670114</v>
       </c>
       <c r="B21" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2781,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2816,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700531</v>
+        <v>700457</v>
       </c>
       <c r="R21" t="n">
-        <v>7283655</v>
+        <v>7283824</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2879,10 +2875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119669149</v>
+        <v>119671043</v>
       </c>
       <c r="B22" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2891,25 +2887,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2926,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700549</v>
+        <v>700268</v>
       </c>
       <c r="R22" t="n">
-        <v>7283677</v>
+        <v>7284015</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2989,10 +2985,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119670346</v>
+        <v>119668856</v>
       </c>
       <c r="B23" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3001,25 +2997,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3036,10 +3032,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700323</v>
+        <v>700493</v>
       </c>
       <c r="R23" t="n">
-        <v>7283904</v>
+        <v>7283574</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3099,7 +3095,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119670283</v>
+        <v>119668636</v>
       </c>
       <c r="B24" t="n">
         <v>91840</v>
@@ -3132,7 +3128,11 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700326</v>
+        <v>700481</v>
       </c>
       <c r="R24" t="n">
-        <v>7283891</v>
+        <v>7283469</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119671624</v>
+        <v>119669114</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3221,25 +3221,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700323</v>
+        <v>700530</v>
       </c>
       <c r="R25" t="n">
-        <v>7283739</v>
+        <v>7283670</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119671053</v>
+        <v>119668092</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700272</v>
+        <v>700436</v>
       </c>
       <c r="R26" t="n">
-        <v>7284020</v>
+        <v>7283456</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119670119</v>
+        <v>119670865</v>
       </c>
       <c r="B27" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700452</v>
+        <v>700262</v>
       </c>
       <c r="R27" t="n">
-        <v>7283825</v>
+        <v>7284000</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3539,10 +3539,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119669350</v>
+        <v>119670372</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>91883</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700547</v>
+        <v>700297</v>
       </c>
       <c r="R28" t="n">
-        <v>7283799</v>
+        <v>7283911</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3622,6 +3622,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>under gammal tallåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119670470</v>
+        <v>119670851</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3661,25 +3666,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3696,10 +3701,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700275</v>
+        <v>700262</v>
       </c>
       <c r="R29" t="n">
-        <v>7283925</v>
+        <v>7283995</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3759,7 +3764,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119669524</v>
+        <v>119671624</v>
       </c>
       <c r="B30" t="n">
         <v>91840</v>
@@ -3806,10 +3811,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700534</v>
+        <v>700323</v>
       </c>
       <c r="R30" t="n">
-        <v>7283826</v>
+        <v>7283739</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3869,10 +3874,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119671393</v>
+        <v>119670237</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3881,25 +3886,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3916,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700329</v>
+        <v>700384</v>
       </c>
       <c r="R31" t="n">
-        <v>7284010</v>
+        <v>7283876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3979,10 +3984,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119668075</v>
+        <v>119668910</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3991,25 +3996,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4026,10 +4031,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700436</v>
+        <v>700502</v>
       </c>
       <c r="R32" t="n">
-        <v>7283449</v>
+        <v>7283590</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4089,10 +4094,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119668856</v>
+        <v>119670144</v>
       </c>
       <c r="B33" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4105,21 +4110,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4136,10 +4141,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700493</v>
+        <v>700448</v>
       </c>
       <c r="R33" t="n">
-        <v>7283574</v>
+        <v>7283840</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4199,10 +4204,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119669380</v>
+        <v>119670358</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4211,25 +4216,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4246,10 +4251,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700532</v>
+        <v>700315</v>
       </c>
       <c r="R34" t="n">
-        <v>7283795</v>
+        <v>7283907</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4314,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119670645</v>
+        <v>119669103</v>
       </c>
       <c r="B35" t="n">
         <v>91840</v>
@@ -4356,10 +4361,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700279</v>
+        <v>700544</v>
       </c>
       <c r="R35" t="n">
-        <v>7283952</v>
+        <v>7283659</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4419,10 +4424,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119670333</v>
+        <v>119670659</v>
       </c>
       <c r="B36" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4431,25 +4436,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4466,10 +4471,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700318</v>
+        <v>700260</v>
       </c>
       <c r="R36" t="n">
-        <v>7283895</v>
+        <v>7283959</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4529,10 +4534,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119670851</v>
+        <v>119669620</v>
       </c>
       <c r="B37" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4541,25 +4546,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4576,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700262</v>
+        <v>700508</v>
       </c>
       <c r="R37" t="n">
-        <v>7283995</v>
+        <v>7283824</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4639,10 +4644,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119668747</v>
+        <v>119669250</v>
       </c>
       <c r="B38" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4651,25 +4656,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4686,10 +4691,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700491</v>
+        <v>700565</v>
       </c>
       <c r="R38" t="n">
-        <v>7283496</v>
+        <v>7283709</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4749,10 +4754,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119671463</v>
+        <v>119669399</v>
       </c>
       <c r="B39" t="n">
-        <v>91834</v>
+        <v>91883</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4765,21 +4770,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4796,10 +4801,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700292</v>
+        <v>700529</v>
       </c>
       <c r="R39" t="n">
-        <v>7283983</v>
+        <v>7283801</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4859,10 +4864,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119669066</v>
+        <v>119668514</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4871,25 +4876,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4906,10 +4911,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700525</v>
+        <v>700458</v>
       </c>
       <c r="R40" t="n">
-        <v>7283654</v>
+        <v>7283459</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4969,10 +4974,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119669112</v>
+        <v>119669071</v>
       </c>
       <c r="B41" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4981,25 +4986,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5016,10 +5021,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700539</v>
+        <v>700531</v>
       </c>
       <c r="R41" t="n">
-        <v>7283665</v>
+        <v>7283655</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5079,7 +5084,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119668829</v>
+        <v>119669058</v>
       </c>
       <c r="B42" t="n">
         <v>91840</v>
@@ -5126,10 +5131,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700478</v>
+        <v>700528</v>
       </c>
       <c r="R42" t="n">
-        <v>7283522</v>
+        <v>7283648</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5189,10 +5194,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119669670</v>
+        <v>119670207</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5201,25 +5206,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5236,10 +5241,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700494</v>
+        <v>700444</v>
       </c>
       <c r="R43" t="n">
-        <v>7283824</v>
+        <v>7283897</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5299,10 +5304,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119669063</v>
+        <v>119670119</v>
       </c>
       <c r="B44" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5311,25 +5316,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5346,10 +5351,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700527</v>
+        <v>700452</v>
       </c>
       <c r="R44" t="n">
-        <v>7283650</v>
+        <v>7283825</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5409,10 +5414,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119671431</v>
+        <v>119670333</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5421,25 +5426,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5456,10 +5461,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>700310</v>
+        <v>700318</v>
       </c>
       <c r="R45" t="n">
-        <v>7283984</v>
+        <v>7283895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5519,10 +5524,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119669503</v>
+        <v>119668709</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5531,25 +5536,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5566,10 +5571,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700527</v>
+        <v>700480</v>
       </c>
       <c r="R46" t="n">
-        <v>7283820</v>
+        <v>7283480</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5629,10 +5634,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119668598</v>
+        <v>119669380</v>
       </c>
       <c r="B47" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5641,25 +5646,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5676,10 +5681,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700468</v>
+        <v>700532</v>
       </c>
       <c r="R47" t="n">
-        <v>7283473</v>
+        <v>7283795</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5739,10 +5744,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119670129</v>
+        <v>119671626</v>
       </c>
       <c r="B48" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5751,25 +5756,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5786,10 +5791,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700456</v>
+        <v>700323</v>
       </c>
       <c r="R48" t="n">
-        <v>7283838</v>
+        <v>7283739</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5849,10 +5854,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119669445</v>
+        <v>119668690</v>
       </c>
       <c r="B49" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5861,25 +5866,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5896,10 +5901,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700524</v>
+        <v>700485</v>
       </c>
       <c r="R49" t="n">
-        <v>7283812</v>
+        <v>7283480</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5959,10 +5964,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119671219</v>
+        <v>119670220</v>
       </c>
       <c r="B50" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5971,25 +5976,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6006,10 +6011,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700316</v>
+        <v>700396</v>
       </c>
       <c r="R50" t="n">
-        <v>7284044</v>
+        <v>7283874</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6069,10 +6074,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119669106</v>
+        <v>119669392</v>
       </c>
       <c r="B51" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6085,21 +6090,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6116,10 +6121,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700538</v>
+        <v>700529</v>
       </c>
       <c r="R51" t="n">
-        <v>7283663</v>
+        <v>7283801</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6179,10 +6184,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119670984</v>
+        <v>119670567</v>
       </c>
       <c r="B52" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6191,25 +6196,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6226,10 +6231,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700278</v>
+        <v>700267</v>
       </c>
       <c r="R52" t="n">
-        <v>7283995</v>
+        <v>7283939</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6289,7 +6294,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119671646</v>
+        <v>119668728</v>
       </c>
       <c r="B53" t="n">
         <v>91834</v>
@@ -6336,10 +6341,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700327</v>
+        <v>700480</v>
       </c>
       <c r="R53" t="n">
-        <v>7283730</v>
+        <v>7283482</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6399,7 +6404,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119671007</v>
+        <v>119668966</v>
       </c>
       <c r="B54" t="n">
         <v>91832</v>
@@ -6432,7 +6437,11 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6446,10 +6455,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700286</v>
+        <v>700497</v>
       </c>
       <c r="R54" t="n">
-        <v>7284004</v>
+        <v>7283615</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6509,10 +6518,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119670207</v>
+        <v>119670746</v>
       </c>
       <c r="B55" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6525,21 +6534,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6556,10 +6565,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700444</v>
+        <v>700272</v>
       </c>
       <c r="R55" t="n">
-        <v>7283897</v>
+        <v>7283984</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6619,10 +6628,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119670911</v>
+        <v>119669590</v>
       </c>
       <c r="B56" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6631,25 +6640,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6666,10 +6675,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700271</v>
+        <v>700511</v>
       </c>
       <c r="R56" t="n">
-        <v>7283996</v>
+        <v>7283834</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6729,10 +6738,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119670580</v>
+        <v>119671069</v>
       </c>
       <c r="B57" t="n">
-        <v>89633</v>
+        <v>91852</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6741,25 +6750,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6776,10 +6785,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700268</v>
+        <v>700296</v>
       </c>
       <c r="R57" t="n">
-        <v>7283948</v>
+        <v>7284015</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6839,10 +6848,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119670237</v>
+        <v>119669503</v>
       </c>
       <c r="B58" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6851,25 +6860,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6886,10 +6895,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700384</v>
+        <v>700527</v>
       </c>
       <c r="R58" t="n">
-        <v>7283876</v>
+        <v>7283820</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6949,10 +6958,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119670970</v>
+        <v>119669445</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6961,25 +6970,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6996,10 +7005,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700273</v>
+        <v>700524</v>
       </c>
       <c r="R59" t="n">
-        <v>7283993</v>
+        <v>7283812</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7059,7 +7068,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119670438</v>
+        <v>119671618</v>
       </c>
       <c r="B60" t="n">
         <v>91840</v>
@@ -7106,10 +7115,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700274</v>
+        <v>700324</v>
       </c>
       <c r="R60" t="n">
-        <v>7283915</v>
+        <v>7283744</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7169,10 +7178,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119669071</v>
+        <v>119669337</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7181,25 +7190,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7216,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700531</v>
+        <v>700544</v>
       </c>
       <c r="R61" t="n">
-        <v>7283655</v>
+        <v>7283794</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7279,10 +7288,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119668503</v>
+        <v>119669004</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7295,21 +7304,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7326,10 +7335,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700436</v>
+        <v>700498</v>
       </c>
       <c r="R62" t="n">
-        <v>7283469</v>
+        <v>7283624</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7389,7 +7398,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119668573</v>
+        <v>119670772</v>
       </c>
       <c r="B63" t="n">
         <v>91840</v>
@@ -7436,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700462</v>
+        <v>700279</v>
       </c>
       <c r="R63" t="n">
-        <v>7283460</v>
+        <v>7283983</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7499,7 +7508,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119670785</v>
+        <v>119669670</v>
       </c>
       <c r="B64" t="n">
         <v>91840</v>
@@ -7546,10 +7555,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700256</v>
+        <v>700494</v>
       </c>
       <c r="R64" t="n">
-        <v>7283992</v>
+        <v>7283824</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7609,10 +7618,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119669038</v>
+        <v>119671393</v>
       </c>
       <c r="B65" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7625,21 +7634,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7656,10 +7665,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700479</v>
+        <v>700329</v>
       </c>
       <c r="R65" t="n">
-        <v>7283639</v>
+        <v>7284010</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7719,10 +7728,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119670195</v>
+        <v>119671608</v>
       </c>
       <c r="B66" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7731,25 +7740,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7766,10 +7775,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700444</v>
+        <v>700327</v>
       </c>
       <c r="R66" t="n">
-        <v>7283887</v>
+        <v>7283760</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7829,10 +7838,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119669147</v>
+        <v>119669370</v>
       </c>
       <c r="B67" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7845,21 +7854,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7876,10 +7885,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700546</v>
+        <v>700533</v>
       </c>
       <c r="R67" t="n">
-        <v>7283682</v>
+        <v>7283795</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7939,7 +7948,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119671088</v>
+        <v>119670129</v>
       </c>
       <c r="B68" t="n">
         <v>91832</v>
@@ -7986,10 +7995,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700306</v>
+        <v>700456</v>
       </c>
       <c r="R68" t="n">
-        <v>7283997</v>
+        <v>7283838</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8049,7 +8058,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119671104</v>
+        <v>119670794</v>
       </c>
       <c r="B69" t="n">
         <v>91832</v>
@@ -8096,10 +8105,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700299</v>
+        <v>700259</v>
       </c>
       <c r="R69" t="n">
-        <v>7284034</v>
+        <v>7283993</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8159,10 +8168,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119671327</v>
+        <v>119670438</v>
       </c>
       <c r="B70" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8171,25 +8180,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8206,10 +8215,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700332</v>
+        <v>700274</v>
       </c>
       <c r="R70" t="n">
-        <v>7284034</v>
+        <v>7283915</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8269,10 +8278,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119670717</v>
+        <v>119671219</v>
       </c>
       <c r="B71" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8281,25 +8290,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8316,10 +8325,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700303</v>
+        <v>700316</v>
       </c>
       <c r="R71" t="n">
-        <v>7283965</v>
+        <v>7284044</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8379,10 +8388,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119671159</v>
+        <v>119670801</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8391,25 +8400,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8426,10 +8435,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700313</v>
+        <v>700262</v>
       </c>
       <c r="R72" t="n">
-        <v>7284032</v>
+        <v>7283995</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8489,10 +8498,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119669004</v>
+        <v>119671327</v>
       </c>
       <c r="B73" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8501,25 +8510,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8536,10 +8545,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700498</v>
+        <v>700332</v>
       </c>
       <c r="R73" t="n">
-        <v>7283624</v>
+        <v>7284034</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8599,10 +8608,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119671626</v>
+        <v>119669000</v>
       </c>
       <c r="B74" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8615,21 +8624,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8646,10 +8655,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700323</v>
+        <v>700509</v>
       </c>
       <c r="R74" t="n">
-        <v>7283739</v>
+        <v>7283621</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8709,10 +8718,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119670220</v>
+        <v>119668797</v>
       </c>
       <c r="B75" t="n">
-        <v>91852</v>
+        <v>91883</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8721,25 +8730,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8756,10 +8765,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700396</v>
+        <v>700473</v>
       </c>
       <c r="R75" t="n">
-        <v>7283874</v>
+        <v>7283509</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8792,6 +8801,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Under gammal tallåga!</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8819,10 +8833,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119671043</v>
+        <v>119669350</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8831,25 +8845,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8866,10 +8880,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700268</v>
+        <v>700547</v>
       </c>
       <c r="R76" t="n">
-        <v>7284015</v>
+        <v>7283799</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8929,10 +8943,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119669399</v>
+        <v>119668926</v>
       </c>
       <c r="B77" t="n">
-        <v>91883</v>
+        <v>91884</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8945,21 +8959,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8976,10 +8990,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700529</v>
+        <v>700502</v>
       </c>
       <c r="R77" t="n">
-        <v>7283801</v>
+        <v>7283590</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9039,7 +9053,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119669419</v>
+        <v>119668423</v>
       </c>
       <c r="B78" t="n">
         <v>91832</v>
@@ -9086,10 +9100,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700519</v>
+        <v>700431</v>
       </c>
       <c r="R78" t="n">
-        <v>7283805</v>
+        <v>7283462</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9149,10 +9163,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119671583</v>
+        <v>119670645</v>
       </c>
       <c r="B79" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9161,25 +9175,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9196,10 +9210,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700309</v>
+        <v>700279</v>
       </c>
       <c r="R79" t="n">
-        <v>7283778</v>
+        <v>7283952</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9259,7 +9273,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119668760</v>
+        <v>119668875</v>
       </c>
       <c r="B80" t="n">
         <v>91840</v>
@@ -9306,10 +9320,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700485</v>
+        <v>700491</v>
       </c>
       <c r="R80" t="n">
-        <v>7283507</v>
+        <v>7283580</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9369,7 +9383,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119669592</v>
+        <v>119668829</v>
       </c>
       <c r="B81" t="n">
         <v>91840</v>
@@ -9416,10 +9430,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700511</v>
+        <v>700478</v>
       </c>
       <c r="R81" t="n">
-        <v>7283834</v>
+        <v>7283522</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9479,7 +9493,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119670567</v>
+        <v>119669143</v>
       </c>
       <c r="B82" t="n">
         <v>91840</v>
@@ -9526,10 +9540,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700267</v>
+        <v>700542</v>
       </c>
       <c r="R82" t="n">
-        <v>7283939</v>
+        <v>7283681</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9589,7 +9603,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119669138</v>
+        <v>119670283</v>
       </c>
       <c r="B83" t="n">
         <v>91840</v>
@@ -9636,10 +9650,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700540</v>
+        <v>700326</v>
       </c>
       <c r="R83" t="n">
-        <v>7283677</v>
+        <v>7283891</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9699,10 +9713,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119671571</v>
+        <v>119670540</v>
       </c>
       <c r="B84" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9715,21 +9729,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9746,10 +9760,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700318</v>
+        <v>700270</v>
       </c>
       <c r="R84" t="n">
-        <v>7283782</v>
+        <v>7283931</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9809,10 +9823,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119670163</v>
+        <v>119670998</v>
       </c>
       <c r="B85" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9825,21 +9839,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9856,10 +9870,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>700444</v>
+        <v>700286</v>
       </c>
       <c r="R85" t="n">
-        <v>7283880</v>
+        <v>7283999</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9919,10 +9933,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119669114</v>
+        <v>119669515</v>
       </c>
       <c r="B86" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9931,25 +9945,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9966,10 +9980,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>700530</v>
+        <v>700532</v>
       </c>
       <c r="R86" t="n">
-        <v>7283670</v>
+        <v>7283821</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10029,7 +10043,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119669058</v>
+        <v>119668849</v>
       </c>
       <c r="B87" t="n">
         <v>91840</v>
@@ -10076,10 +10090,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700528</v>
+        <v>700480</v>
       </c>
       <c r="R87" t="n">
-        <v>7283648</v>
+        <v>7283558</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10139,10 +10153,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119669297</v>
+        <v>119669038</v>
       </c>
       <c r="B88" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10155,21 +10169,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10186,10 +10200,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700594</v>
+        <v>700479</v>
       </c>
       <c r="R88" t="n">
-        <v>7283740</v>
+        <v>7283639</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10249,10 +10263,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119671635</v>
+        <v>119669106</v>
       </c>
       <c r="B89" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10261,25 +10275,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10296,10 +10310,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>700317</v>
+        <v>700538</v>
       </c>
       <c r="R89" t="n">
-        <v>7283727</v>
+        <v>7283663</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10359,10 +10373,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119670670</v>
+        <v>119670886</v>
       </c>
       <c r="B90" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10371,25 +10385,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10409,7 +10423,7 @@
         <v>700264</v>
       </c>
       <c r="R90" t="n">
-        <v>7283977</v>
+        <v>7283999</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10469,7 +10483,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119668841</v>
+        <v>119669297</v>
       </c>
       <c r="B91" t="n">
         <v>91840</v>
@@ -10516,10 +10530,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>700476</v>
+        <v>700594</v>
       </c>
       <c r="R91" t="n">
-        <v>7283544</v>
+        <v>7283740</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10579,10 +10593,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119671138</v>
+        <v>119671104</v>
       </c>
       <c r="B92" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10591,25 +10605,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10626,10 +10640,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>700311</v>
+        <v>700299</v>
       </c>
       <c r="R92" t="n">
-        <v>7284032</v>
+        <v>7284034</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10689,10 +10703,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119671608</v>
+        <v>119671451</v>
       </c>
       <c r="B93" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10701,25 +10715,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10736,10 +10750,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700327</v>
+        <v>700295</v>
       </c>
       <c r="R93" t="n">
-        <v>7283760</v>
+        <v>7283983</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10799,7 +10813,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119668910</v>
+        <v>119671571</v>
       </c>
       <c r="B94" t="n">
         <v>89633</v>
@@ -10846,10 +10860,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>700502</v>
+        <v>700318</v>
       </c>
       <c r="R94" t="n">
-        <v>7283590</v>
+        <v>7283782</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10909,10 +10923,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119671451</v>
+        <v>119669149</v>
       </c>
       <c r="B95" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10925,21 +10939,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10956,10 +10970,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>700295</v>
+        <v>700549</v>
       </c>
       <c r="R95" t="n">
-        <v>7283983</v>
+        <v>7283677</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11019,10 +11033,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119670865</v>
+        <v>119668747</v>
       </c>
       <c r="B96" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11035,21 +11049,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11066,10 +11080,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>700262</v>
+        <v>700491</v>
       </c>
       <c r="R96" t="n">
-        <v>7284000</v>
+        <v>7283496</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11129,10 +11143,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119670801</v>
+        <v>119671635</v>
       </c>
       <c r="B97" t="n">
-        <v>91844</v>
+        <v>91852</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11141,25 +11155,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11176,10 +11190,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>700262</v>
+        <v>700317</v>
       </c>
       <c r="R97" t="n">
-        <v>7283995</v>
+        <v>7283727</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11239,10 +11253,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119669683</v>
+        <v>119670959</v>
       </c>
       <c r="B98" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11251,25 +11265,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11286,10 +11300,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>700488</v>
+        <v>700274</v>
       </c>
       <c r="R98" t="n">
-        <v>7283816</v>
+        <v>7283995</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11349,10 +11363,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119668849</v>
+        <v>119669471</v>
       </c>
       <c r="B99" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11365,21 +11379,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11396,10 +11410,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>700480</v>
+        <v>700537</v>
       </c>
       <c r="R99" t="n">
-        <v>7283558</v>
+        <v>7283817</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11459,7 +11473,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119669620</v>
+        <v>119670430</v>
       </c>
       <c r="B100" t="n">
         <v>91852</v>
@@ -11506,10 +11520,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>700508</v>
+        <v>700280</v>
       </c>
       <c r="R100" t="n">
-        <v>7283824</v>
+        <v>7283905</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11569,10 +11583,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119668736</v>
+        <v>119669271</v>
       </c>
       <c r="B101" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11581,25 +11595,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11616,10 +11630,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>700474</v>
+        <v>700583</v>
       </c>
       <c r="R101" t="n">
-        <v>7283486</v>
+        <v>7283727</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11679,7 +11693,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119671117</v>
+        <v>119670596</v>
       </c>
       <c r="B102" t="n">
         <v>91832</v>
@@ -11726,10 +11740,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>700298</v>
+        <v>700268</v>
       </c>
       <c r="R102" t="n">
-        <v>7284037</v>
+        <v>7283952</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11789,10 +11803,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119669042</v>
+        <v>119668503</v>
       </c>
       <c r="B103" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11801,25 +11815,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11836,10 +11850,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>700479</v>
+        <v>700436</v>
       </c>
       <c r="R103" t="n">
-        <v>7283639</v>
+        <v>7283469</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11899,10 +11913,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119668728</v>
+        <v>119668593</v>
       </c>
       <c r="B104" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11911,25 +11925,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11946,10 +11960,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>700480</v>
+        <v>700468</v>
       </c>
       <c r="R104" t="n">
-        <v>7283482</v>
+        <v>7283473</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12009,10 +12023,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119671618</v>
+        <v>119670163</v>
       </c>
       <c r="B105" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12021,25 +12035,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12056,10 +12070,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>700324</v>
+        <v>700444</v>
       </c>
       <c r="R105" t="n">
-        <v>7283744</v>
+        <v>7283880</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12119,10 +12133,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119670256</v>
+        <v>119670470</v>
       </c>
       <c r="B106" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12135,21 +12149,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12166,10 +12180,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>700334</v>
+        <v>700275</v>
       </c>
       <c r="R106" t="n">
-        <v>7283862</v>
+        <v>7283925</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12229,10 +12243,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119670259</v>
+        <v>119669592</v>
       </c>
       <c r="B107" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12245,21 +12259,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12276,10 +12290,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>700337</v>
+        <v>700511</v>
       </c>
       <c r="R107" t="n">
-        <v>7283884</v>
+        <v>7283834</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12339,10 +12353,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119670301</v>
+        <v>119669112</v>
       </c>
       <c r="B108" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12351,25 +12365,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12386,10 +12400,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>700314</v>
+        <v>700539</v>
       </c>
       <c r="R108" t="n">
-        <v>7283890</v>
+        <v>7283665</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12449,10 +12463,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119669392</v>
+        <v>119671597</v>
       </c>
       <c r="B109" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12465,21 +12479,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12496,10 +12510,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>700529</v>
+        <v>700315</v>
       </c>
       <c r="R109" t="n">
-        <v>7283801</v>
+        <v>7283776</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12559,10 +12573,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119670746</v>
+        <v>119668736</v>
       </c>
       <c r="B110" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12571,25 +12585,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12606,10 +12620,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>700272</v>
+        <v>700474</v>
       </c>
       <c r="R110" t="n">
-        <v>7283984</v>
+        <v>7283486</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12669,10 +12683,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119670106</v>
+        <v>119669688</v>
       </c>
       <c r="B111" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12681,25 +12695,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12716,10 +12730,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>700463</v>
+        <v>700487</v>
       </c>
       <c r="R111" t="n">
-        <v>7283819</v>
+        <v>7283810</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12779,10 +12793,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119670168</v>
+        <v>119670941</v>
       </c>
       <c r="B112" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12791,25 +12805,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12826,10 +12840,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>700434</v>
+        <v>700274</v>
       </c>
       <c r="R112" t="n">
-        <v>7283885</v>
+        <v>7283997</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12889,10 +12903,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119669515</v>
+        <v>119670670</v>
       </c>
       <c r="B113" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12905,21 +12919,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12936,10 +12950,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>700532</v>
+        <v>700264</v>
       </c>
       <c r="R113" t="n">
-        <v>7283821</v>
+        <v>7283977</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12999,10 +13013,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119668809</v>
+        <v>119670346</v>
       </c>
       <c r="B114" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13015,21 +13029,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13046,10 +13060,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>700481</v>
+        <v>700323</v>
       </c>
       <c r="R114" t="n">
-        <v>7283509</v>
+        <v>7283904</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13109,7 +13123,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119668636</v>
+        <v>119671053</v>
       </c>
       <c r="B115" t="n">
         <v>91840</v>
@@ -13142,11 +13156,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -13160,10 +13170,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>700481</v>
+        <v>700272</v>
       </c>
       <c r="R115" t="n">
-        <v>7283469</v>
+        <v>7284020</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13223,7 +13233,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119670540</v>
+        <v>119670911</v>
       </c>
       <c r="B116" t="n">
         <v>91832</v>
@@ -13270,10 +13280,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>700270</v>
+        <v>700271</v>
       </c>
       <c r="R116" t="n">
-        <v>7283931</v>
+        <v>7283996</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13333,10 +13343,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119669309</v>
+        <v>119669320</v>
       </c>
       <c r="B117" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13345,25 +13355,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13380,10 +13390,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>700595</v>
+        <v>700590</v>
       </c>
       <c r="R117" t="n">
-        <v>7283758</v>
+        <v>7283790</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13443,10 +13453,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119670777</v>
+        <v>119670984</v>
       </c>
       <c r="B118" t="n">
-        <v>92030</v>
+        <v>91832</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13459,21 +13469,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2079</v>
+        <v>4361</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13490,10 +13500,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>700279</v>
+        <v>700278</v>
       </c>
       <c r="R118" t="n">
-        <v>7283988</v>
+        <v>7283995</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13553,10 +13563,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119669674</v>
+        <v>119671431</v>
       </c>
       <c r="B119" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13565,25 +13575,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13600,10 +13610,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>700494</v>
+        <v>700310</v>
       </c>
       <c r="R119" t="n">
-        <v>7283824</v>
+        <v>7283984</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13663,10 +13673,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119668701</v>
+        <v>119669309</v>
       </c>
       <c r="B120" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13679,21 +13689,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13710,10 +13720,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>700485</v>
+        <v>700595</v>
       </c>
       <c r="R120" t="n">
-        <v>7283480</v>
+        <v>7283758</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13773,7 +13783,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119668709</v>
+        <v>119668598</v>
       </c>
       <c r="B121" t="n">
         <v>91856</v>
@@ -13820,10 +13830,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>700480</v>
+        <v>700468</v>
       </c>
       <c r="R121" t="n">
-        <v>7283480</v>
+        <v>7283473</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13883,7 +13893,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119669103</v>
+        <v>119668715</v>
       </c>
       <c r="B122" t="n">
         <v>91840</v>
@@ -13930,10 +13940,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>700544</v>
+        <v>700480</v>
       </c>
       <c r="R122" t="n">
-        <v>7283659</v>
+        <v>7283480</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13993,7 +14003,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119668690</v>
+        <v>119668573</v>
       </c>
       <c r="B123" t="n">
         <v>91840</v>
@@ -14040,10 +14050,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>700485</v>
+        <v>700462</v>
       </c>
       <c r="R123" t="n">
-        <v>7283480</v>
+        <v>7283460</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14103,10 +14113,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119670659</v>
+        <v>119670256</v>
       </c>
       <c r="B124" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14119,21 +14129,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14150,10 +14160,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>700260</v>
+        <v>700334</v>
       </c>
       <c r="R124" t="n">
-        <v>7283959</v>
+        <v>7283862</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14213,10 +14223,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119669634</v>
+        <v>119669063</v>
       </c>
       <c r="B125" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14229,21 +14239,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14260,10 +14270,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>700503</v>
+        <v>700527</v>
       </c>
       <c r="R125" t="n">
-        <v>7283829</v>
+        <v>7283650</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14323,10 +14333,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119669000</v>
+        <v>119670106</v>
       </c>
       <c r="B126" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14335,25 +14345,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14370,10 +14380,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>700509</v>
+        <v>700463</v>
       </c>
       <c r="R126" t="n">
-        <v>7283621</v>
+        <v>7283819</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14433,10 +14443,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119670114</v>
+        <v>119671583</v>
       </c>
       <c r="B127" t="n">
-        <v>91834</v>
+        <v>90807</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14445,25 +14455,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14480,10 +14490,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>700457</v>
+        <v>700309</v>
       </c>
       <c r="R127" t="n">
-        <v>7283824</v>
+        <v>7283778</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14543,10 +14553,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119669320</v>
+        <v>119670153</v>
       </c>
       <c r="B128" t="n">
-        <v>91852</v>
+        <v>92030</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14555,25 +14565,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4366</v>
+        <v>2079</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14590,10 +14600,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>700590</v>
+        <v>700453</v>
       </c>
       <c r="R128" t="n">
-        <v>7283790</v>
+        <v>7283845</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14653,10 +14663,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119668945</v>
+        <v>119668701</v>
       </c>
       <c r="B129" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14665,25 +14675,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14700,10 +14710,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>700493</v>
+        <v>700485</v>
       </c>
       <c r="R129" t="n">
-        <v>7283596</v>
+        <v>7283480</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14763,10 +14773,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119671597</v>
+        <v>119671159</v>
       </c>
       <c r="B130" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14775,25 +14785,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14810,10 +14820,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>700315</v>
+        <v>700313</v>
       </c>
       <c r="R130" t="n">
-        <v>7283776</v>
+        <v>7284032</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14873,10 +14883,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119668797</v>
+        <v>119671088</v>
       </c>
       <c r="B131" t="n">
-        <v>91883</v>
+        <v>91832</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14889,21 +14899,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14920,10 +14930,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>700473</v>
+        <v>700306</v>
       </c>
       <c r="R131" t="n">
-        <v>7283509</v>
+        <v>7283997</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14956,11 +14966,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Under gammal tallåga!</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14988,10 +14993,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119670372</v>
+        <v>119669066</v>
       </c>
       <c r="B132" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15000,25 +15005,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15035,10 +15040,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>700297</v>
+        <v>700525</v>
       </c>
       <c r="R132" t="n">
-        <v>7283911</v>
+        <v>7283654</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15071,11 +15076,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>under gammal tallåga</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15103,10 +15103,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119668926</v>
+        <v>119671007</v>
       </c>
       <c r="B133" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15119,21 +15119,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15150,10 +15150,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>700502</v>
+        <v>700286</v>
       </c>
       <c r="R133" t="n">
-        <v>7283590</v>
+        <v>7284004</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15213,10 +15213,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119670358</v>
+        <v>119668075</v>
       </c>
       <c r="B134" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15225,25 +15225,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15260,10 +15260,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>700315</v>
+        <v>700436</v>
       </c>
       <c r="R134" t="n">
-        <v>7283907</v>
+        <v>7283449</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15323,10 +15323,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119669471</v>
+        <v>119669419</v>
       </c>
       <c r="B135" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15335,25 +15335,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15370,10 +15370,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>700537</v>
+        <v>700519</v>
       </c>
       <c r="R135" t="n">
-        <v>7283817</v>
+        <v>7283805</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15433,10 +15433,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119670430</v>
+        <v>119670970</v>
       </c>
       <c r="B136" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15449,21 +15449,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>700280</v>
+        <v>700273</v>
       </c>
       <c r="R136" t="n">
-        <v>7283905</v>
+        <v>7283993</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15543,10 +15543,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119668834</v>
+        <v>119670230</v>
       </c>
       <c r="B137" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15555,25 +15555,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15590,10 +15590,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>700478</v>
+        <v>700384</v>
       </c>
       <c r="R137" t="n">
-        <v>7283522</v>
+        <v>7283876</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15763,10 +15763,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119669410</v>
+        <v>119669683</v>
       </c>
       <c r="B139" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15775,25 +15775,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15810,10 +15810,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>700511</v>
+        <v>700488</v>
       </c>
       <c r="R139" t="n">
-        <v>7283802</v>
+        <v>7283816</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15873,10 +15873,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119669476</v>
+        <v>119669147</v>
       </c>
       <c r="B140" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15885,25 +15885,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15920,10 +15920,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>700537</v>
+        <v>700546</v>
       </c>
       <c r="R140" t="n">
-        <v>7283817</v>
+        <v>7283682</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15983,10 +15983,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119670772</v>
+        <v>119669674</v>
       </c>
       <c r="B141" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15995,25 +15995,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16030,10 +16030,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>700279</v>
+        <v>700494</v>
       </c>
       <c r="R141" t="n">
-        <v>7283983</v>
+        <v>7283824</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16093,10 +16093,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119669143</v>
+        <v>119670580</v>
       </c>
       <c r="B142" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16105,25 +16105,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16140,10 +16140,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>700542</v>
+        <v>700268</v>
       </c>
       <c r="R142" t="n">
-        <v>7283681</v>
+        <v>7283948</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16203,10 +16203,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119669688</v>
+        <v>119669042</v>
       </c>
       <c r="B143" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16215,25 +16215,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16250,10 +16250,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>700487</v>
+        <v>700479</v>
       </c>
       <c r="R143" t="n">
-        <v>7283810</v>
+        <v>7283639</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16313,10 +16313,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119670153</v>
+        <v>119669410</v>
       </c>
       <c r="B144" t="n">
-        <v>92030</v>
+        <v>91834</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16329,21 +16329,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16360,10 +16360,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>700453</v>
+        <v>700511</v>
       </c>
       <c r="R144" t="n">
-        <v>7283845</v>
+        <v>7283802</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16423,10 +16423,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119670941</v>
+        <v>119668809</v>
       </c>
       <c r="B145" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16435,25 +16435,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16470,10 +16470,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>700274</v>
+        <v>700481</v>
       </c>
       <c r="R145" t="n">
-        <v>7283997</v>
+        <v>7283509</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16533,7 +16533,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119670230</v>
+        <v>119669138</v>
       </c>
       <c r="B146" t="n">
         <v>91840</v>
@@ -16580,10 +16580,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>700384</v>
+        <v>700540</v>
       </c>
       <c r="R146" t="n">
-        <v>7283876</v>
+        <v>7283677</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16643,10 +16643,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119668423</v>
+        <v>119669524</v>
       </c>
       <c r="B147" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16655,25 +16655,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16690,10 +16690,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>700431</v>
+        <v>700534</v>
       </c>
       <c r="R147" t="n">
-        <v>7283462</v>
+        <v>7283826</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16753,10 +16753,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119670794</v>
+        <v>119669634</v>
       </c>
       <c r="B148" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16765,25 +16765,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16800,10 +16800,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>700259</v>
+        <v>700503</v>
       </c>
       <c r="R148" t="n">
-        <v>7283993</v>
+        <v>7283829</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16863,10 +16863,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119668593</v>
+        <v>119670259</v>
       </c>
       <c r="B149" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16879,21 +16879,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16910,10 +16910,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>700468</v>
+        <v>700337</v>
       </c>
       <c r="R149" t="n">
-        <v>7283473</v>
+        <v>7283884</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16973,10 +16973,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119669250</v>
+        <v>119671138</v>
       </c>
       <c r="B150" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16989,21 +16989,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17020,10 +17020,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>700565</v>
+        <v>700311</v>
       </c>
       <c r="R150" t="n">
-        <v>7283709</v>
+        <v>7284032</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17083,10 +17083,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119670886</v>
+        <v>119668945</v>
       </c>
       <c r="B151" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17095,25 +17095,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17130,10 +17130,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>700264</v>
+        <v>700493</v>
       </c>
       <c r="R151" t="n">
-        <v>7283999</v>
+        <v>7283596</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17193,7 +17193,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119670959</v>
+        <v>119670490</v>
       </c>
       <c r="B152" t="n">
         <v>91832</v>
@@ -17240,10 +17240,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>700274</v>
+        <v>700275</v>
       </c>
       <c r="R152" t="n">
-        <v>7283995</v>
+        <v>7283925</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -2765,10 +2765,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119670114</v>
+        <v>119668636</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2777,28 +2777,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2812,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700457</v>
+        <v>700481</v>
       </c>
       <c r="R21" t="n">
-        <v>7283824</v>
+        <v>7283469</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2875,10 +2879,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119671043</v>
+        <v>119670114</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2887,25 +2891,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2926,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700268</v>
+        <v>700457</v>
       </c>
       <c r="R22" t="n">
-        <v>7284015</v>
+        <v>7283824</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2985,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119668856</v>
+        <v>119671043</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2997,25 +3001,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3032,10 +3036,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700493</v>
+        <v>700268</v>
       </c>
       <c r="R23" t="n">
-        <v>7283574</v>
+        <v>7284015</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3095,10 +3099,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119668636</v>
+        <v>119668856</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3107,32 +3111,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700481</v>
+        <v>700493</v>
       </c>
       <c r="R24" t="n">
-        <v>7283469</v>
+        <v>7283574</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -7178,10 +7178,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119669337</v>
+        <v>119669004</v>
       </c>
       <c r="B61" t="n">
-        <v>92030</v>
+        <v>91852</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7190,25 +7190,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>4366</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700544</v>
+        <v>700498</v>
       </c>
       <c r="R61" t="n">
-        <v>7283794</v>
+        <v>7283624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7288,10 +7288,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119669004</v>
+        <v>119669670</v>
       </c>
       <c r="B62" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7304,21 +7304,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7335,10 +7335,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700498</v>
+        <v>700494</v>
       </c>
       <c r="R62" t="n">
-        <v>7283624</v>
+        <v>7283824</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7398,10 +7398,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119670772</v>
+        <v>119669337</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7410,25 +7410,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700279</v>
+        <v>700544</v>
       </c>
       <c r="R63" t="n">
-        <v>7283983</v>
+        <v>7283794</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7508,7 +7508,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119669670</v>
+        <v>119670772</v>
       </c>
       <c r="B64" t="n">
         <v>91840</v>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700494</v>
+        <v>700279</v>
       </c>
       <c r="R64" t="n">
-        <v>7283824</v>
+        <v>7283983</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8943,10 +8943,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119668926</v>
+        <v>119668423</v>
       </c>
       <c r="B77" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8959,21 +8959,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8990,10 +8990,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700502</v>
+        <v>700431</v>
       </c>
       <c r="R77" t="n">
-        <v>7283590</v>
+        <v>7283462</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9053,10 +9053,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119668423</v>
+        <v>119670645</v>
       </c>
       <c r="B78" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9065,25 +9065,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9100,10 +9100,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700431</v>
+        <v>700279</v>
       </c>
       <c r="R78" t="n">
-        <v>7283462</v>
+        <v>7283952</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9163,7 +9163,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119670645</v>
+        <v>119668875</v>
       </c>
       <c r="B79" t="n">
         <v>91840</v>
@@ -9210,10 +9210,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700279</v>
+        <v>700491</v>
       </c>
       <c r="R79" t="n">
-        <v>7283952</v>
+        <v>7283580</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119668875</v>
+        <v>119668829</v>
       </c>
       <c r="B80" t="n">
         <v>91840</v>
@@ -9320,10 +9320,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700491</v>
+        <v>700478</v>
       </c>
       <c r="R80" t="n">
-        <v>7283580</v>
+        <v>7283522</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9383,7 +9383,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119668829</v>
+        <v>119669143</v>
       </c>
       <c r="B81" t="n">
         <v>91840</v>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700478</v>
+        <v>700542</v>
       </c>
       <c r="R81" t="n">
-        <v>7283522</v>
+        <v>7283681</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9493,10 +9493,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119669143</v>
+        <v>119670540</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9505,25 +9505,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700542</v>
+        <v>700270</v>
       </c>
       <c r="R82" t="n">
-        <v>7283681</v>
+        <v>7283931</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9603,10 +9603,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119670283</v>
+        <v>119668926</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9615,25 +9615,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700326</v>
+        <v>700502</v>
       </c>
       <c r="R83" t="n">
-        <v>7283891</v>
+        <v>7283590</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9713,10 +9713,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119670540</v>
+        <v>119670283</v>
       </c>
       <c r="B84" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9725,25 +9725,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9760,10 +9760,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700270</v>
+        <v>700326</v>
       </c>
       <c r="R84" t="n">
-        <v>7283931</v>
+        <v>7283891</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9933,10 +9933,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119669515</v>
+        <v>119668849</v>
       </c>
       <c r="B86" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9949,21 +9949,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9980,10 +9980,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>700532</v>
+        <v>700480</v>
       </c>
       <c r="R86" t="n">
-        <v>7283821</v>
+        <v>7283558</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10043,10 +10043,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119668849</v>
+        <v>119669515</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10059,21 +10059,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10090,10 +10090,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700480</v>
+        <v>700532</v>
       </c>
       <c r="R87" t="n">
-        <v>7283558</v>
+        <v>7283821</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119671117</v>
+        <v>119669592</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700298</v>
+        <v>700511</v>
       </c>
       <c r="R4" t="n">
-        <v>7284037</v>
+        <v>7283834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119670195</v>
+        <v>119668503</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700444</v>
+        <v>700436</v>
       </c>
       <c r="R5" t="n">
-        <v>7283887</v>
+        <v>7283469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119668760</v>
+        <v>119669590</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700485</v>
+        <v>700511</v>
       </c>
       <c r="R6" t="n">
-        <v>7283507</v>
+        <v>7283834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119669476</v>
+        <v>119668910</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700537</v>
+        <v>700502</v>
       </c>
       <c r="R7" t="n">
-        <v>7283817</v>
+        <v>7283590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119668834</v>
+        <v>119668573</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,25 +1347,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700478</v>
+        <v>700462</v>
       </c>
       <c r="R8" t="n">
-        <v>7283522</v>
+        <v>7283460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119670353</v>
+        <v>119668856</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,25 +1457,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700315</v>
+        <v>700493</v>
       </c>
       <c r="R9" t="n">
-        <v>7283907</v>
+        <v>7283574</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119670717</v>
+        <v>119671053</v>
       </c>
       <c r="B10" t="n">
         <v>91840</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700303</v>
+        <v>700272</v>
       </c>
       <c r="R10" t="n">
-        <v>7283965</v>
+        <v>7284020</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119671463</v>
+        <v>119670984</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700292</v>
+        <v>700278</v>
       </c>
       <c r="R11" t="n">
-        <v>7283983</v>
+        <v>7283995</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119670777</v>
+        <v>119669524</v>
       </c>
       <c r="B12" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,25 +1787,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700279</v>
+        <v>700534</v>
       </c>
       <c r="R12" t="n">
-        <v>7283988</v>
+        <v>7283826</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119668841</v>
+        <v>119670470</v>
       </c>
       <c r="B13" t="n">
         <v>91840</v>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700476</v>
+        <v>700275</v>
       </c>
       <c r="R13" t="n">
-        <v>7283544</v>
+        <v>7283925</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119669073</v>
+        <v>119670746</v>
       </c>
       <c r="B14" t="n">
-        <v>91826</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700531</v>
+        <v>700272</v>
       </c>
       <c r="R14" t="n">
-        <v>7283655</v>
+        <v>7283984</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119669430</v>
+        <v>119670959</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2117,25 +2117,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700515</v>
+        <v>700274</v>
       </c>
       <c r="R15" t="n">
-        <v>7283808</v>
+        <v>7283995</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119670785</v>
+        <v>119669419</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2227,25 +2227,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700256</v>
+        <v>700519</v>
       </c>
       <c r="R16" t="n">
-        <v>7283992</v>
+        <v>7283805</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119670301</v>
+        <v>119670283</v>
       </c>
       <c r="B17" t="n">
         <v>91840</v>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700314</v>
+        <v>700326</v>
       </c>
       <c r="R17" t="n">
-        <v>7283890</v>
+        <v>7283891</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119670168</v>
+        <v>119669114</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2447,25 +2447,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700434</v>
+        <v>700530</v>
       </c>
       <c r="R18" t="n">
-        <v>7283885</v>
+        <v>7283670</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119670458</v>
+        <v>119670106</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2557,25 +2557,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700272</v>
+        <v>700463</v>
       </c>
       <c r="R19" t="n">
-        <v>7283921</v>
+        <v>7283819</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119671646</v>
+        <v>119669471</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2667,25 +2667,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700327</v>
+        <v>700537</v>
       </c>
       <c r="R20" t="n">
-        <v>7283730</v>
+        <v>7283817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119668636</v>
+        <v>119668841</v>
       </c>
       <c r="B21" t="n">
         <v>91840</v>
@@ -2798,11 +2798,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2816,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700481</v>
+        <v>700476</v>
       </c>
       <c r="R21" t="n">
-        <v>7283469</v>
+        <v>7283544</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2879,7 +2875,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119670114</v>
+        <v>119669410</v>
       </c>
       <c r="B22" t="n">
         <v>91834</v>
@@ -2926,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700457</v>
+        <v>700511</v>
       </c>
       <c r="R22" t="n">
-        <v>7283824</v>
+        <v>7283802</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2989,10 +2985,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119671043</v>
+        <v>119670237</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3001,25 +2997,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3036,10 +3032,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700268</v>
+        <v>700384</v>
       </c>
       <c r="R23" t="n">
-        <v>7284015</v>
+        <v>7283876</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3099,7 +3095,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119668856</v>
+        <v>119669445</v>
       </c>
       <c r="B24" t="n">
         <v>91834</v>
@@ -3146,10 +3142,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700493</v>
+        <v>700524</v>
       </c>
       <c r="R24" t="n">
-        <v>7283574</v>
+        <v>7283812</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3209,7 +3205,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119669114</v>
+        <v>119670114</v>
       </c>
       <c r="B25" t="n">
         <v>91834</v>
@@ -3256,10 +3252,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700530</v>
+        <v>700457</v>
       </c>
       <c r="R25" t="n">
-        <v>7283670</v>
+        <v>7283824</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3319,10 +3315,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119668092</v>
+        <v>119670596</v>
       </c>
       <c r="B26" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3335,21 +3331,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3366,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700436</v>
+        <v>700268</v>
       </c>
       <c r="R26" t="n">
-        <v>7283456</v>
+        <v>7283952</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3429,10 +3425,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119670865</v>
+        <v>119671597</v>
       </c>
       <c r="B27" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3445,21 +3441,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3476,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700262</v>
+        <v>700315</v>
       </c>
       <c r="R27" t="n">
-        <v>7284000</v>
+        <v>7283776</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3539,10 +3535,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119670372</v>
+        <v>119671431</v>
       </c>
       <c r="B28" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3551,25 +3547,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3586,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700297</v>
+        <v>700310</v>
       </c>
       <c r="R28" t="n">
-        <v>7283911</v>
+        <v>7283984</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3622,11 +3618,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>under gammal tallåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,10 +3645,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119670851</v>
+        <v>119669309</v>
       </c>
       <c r="B29" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3670,21 +3661,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3701,10 +3692,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700262</v>
+        <v>700595</v>
       </c>
       <c r="R29" t="n">
-        <v>7283995</v>
+        <v>7283758</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3764,7 +3755,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119671624</v>
+        <v>119670735</v>
       </c>
       <c r="B30" t="n">
         <v>91840</v>
@@ -3811,10 +3802,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700323</v>
+        <v>700264</v>
       </c>
       <c r="R30" t="n">
-        <v>7283739</v>
+        <v>7283977</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3874,10 +3865,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119670237</v>
+        <v>119670168</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3886,25 +3877,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700384</v>
+        <v>700434</v>
       </c>
       <c r="R31" t="n">
-        <v>7283876</v>
+        <v>7283885</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3984,10 +3975,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119668910</v>
+        <v>119670353</v>
       </c>
       <c r="B32" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3996,25 +3987,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4031,10 +4022,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700502</v>
+        <v>700315</v>
       </c>
       <c r="R32" t="n">
-        <v>7283590</v>
+        <v>7283907</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4094,10 +4085,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119670144</v>
+        <v>119671043</v>
       </c>
       <c r="B33" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4106,25 +4097,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4141,10 +4132,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700448</v>
+        <v>700268</v>
       </c>
       <c r="R33" t="n">
-        <v>7283840</v>
+        <v>7284015</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4204,10 +4195,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119670358</v>
+        <v>119669066</v>
       </c>
       <c r="B34" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4216,25 +4207,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4251,10 +4242,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700315</v>
+        <v>700525</v>
       </c>
       <c r="R34" t="n">
-        <v>7283907</v>
+        <v>7283654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4314,7 +4305,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119669103</v>
+        <v>119671138</v>
       </c>
       <c r="B35" t="n">
         <v>91840</v>
@@ -4361,10 +4352,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700544</v>
+        <v>700311</v>
       </c>
       <c r="R35" t="n">
-        <v>7283659</v>
+        <v>7284032</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4424,10 +4415,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119670659</v>
+        <v>119670144</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4436,25 +4427,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4471,10 +4462,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700260</v>
+        <v>700448</v>
       </c>
       <c r="R36" t="n">
-        <v>7283959</v>
+        <v>7283840</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4534,10 +4525,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119669620</v>
+        <v>119669674</v>
       </c>
       <c r="B37" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4546,25 +4537,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4581,7 +4572,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700508</v>
+        <v>700494</v>
       </c>
       <c r="R37" t="n">
         <v>7283824</v>
@@ -4644,10 +4635,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119669250</v>
+        <v>119670785</v>
       </c>
       <c r="B38" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4660,21 +4651,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4691,10 +4682,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700565</v>
+        <v>700256</v>
       </c>
       <c r="R38" t="n">
-        <v>7283709</v>
+        <v>7283992</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4754,10 +4745,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119669399</v>
+        <v>119668690</v>
       </c>
       <c r="B39" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4766,25 +4757,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4801,10 +4792,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700529</v>
+        <v>700485</v>
       </c>
       <c r="R39" t="n">
-        <v>7283801</v>
+        <v>7283480</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4864,7 +4855,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119668514</v>
+        <v>119668747</v>
       </c>
       <c r="B40" t="n">
         <v>91834</v>
@@ -4911,10 +4902,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700458</v>
+        <v>700491</v>
       </c>
       <c r="R40" t="n">
-        <v>7283459</v>
+        <v>7283496</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4974,10 +4965,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119669071</v>
+        <v>119669106</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4986,25 +4977,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5021,10 +5012,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700531</v>
+        <v>700538</v>
       </c>
       <c r="R41" t="n">
-        <v>7283655</v>
+        <v>7283663</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5084,10 +5075,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119669058</v>
+        <v>119669073</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5096,25 +5087,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5131,10 +5122,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700528</v>
+        <v>700531</v>
       </c>
       <c r="R42" t="n">
-        <v>7283648</v>
+        <v>7283655</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5194,10 +5185,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119670207</v>
+        <v>119670540</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5210,21 +5201,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5241,10 +5232,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700444</v>
+        <v>700270</v>
       </c>
       <c r="R43" t="n">
-        <v>7283897</v>
+        <v>7283931</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5304,10 +5295,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119670119</v>
+        <v>119670580</v>
       </c>
       <c r="B44" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5320,21 +5311,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5351,10 +5342,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700452</v>
+        <v>700268</v>
       </c>
       <c r="R44" t="n">
-        <v>7283825</v>
+        <v>7283948</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5414,10 +5405,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119670333</v>
+        <v>119669103</v>
       </c>
       <c r="B45" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5426,25 +5417,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5461,10 +5452,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>700318</v>
+        <v>700544</v>
       </c>
       <c r="R45" t="n">
-        <v>7283895</v>
+        <v>7283659</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5524,10 +5515,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119668709</v>
+        <v>119669143</v>
       </c>
       <c r="B46" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5536,25 +5527,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5571,10 +5562,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700480</v>
+        <v>700542</v>
       </c>
       <c r="R46" t="n">
-        <v>7283480</v>
+        <v>7283681</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5634,10 +5625,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119669380</v>
+        <v>119670207</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5646,25 +5637,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5681,10 +5672,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700532</v>
+        <v>700444</v>
       </c>
       <c r="R47" t="n">
-        <v>7283795</v>
+        <v>7283897</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5744,10 +5735,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119671626</v>
+        <v>119669683</v>
       </c>
       <c r="B48" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5760,21 +5751,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5791,10 +5782,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700323</v>
+        <v>700488</v>
       </c>
       <c r="R48" t="n">
-        <v>7283739</v>
+        <v>7283816</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5854,10 +5845,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119668690</v>
+        <v>119670259</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5870,21 +5861,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5901,10 +5892,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700485</v>
+        <v>700337</v>
       </c>
       <c r="R49" t="n">
-        <v>7283480</v>
+        <v>7283884</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5964,10 +5955,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119670220</v>
+        <v>119670801</v>
       </c>
       <c r="B50" t="n">
-        <v>91852</v>
+        <v>91844</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5976,25 +5967,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6011,10 +6002,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700396</v>
+        <v>700262</v>
       </c>
       <c r="R50" t="n">
-        <v>7283874</v>
+        <v>7283995</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6074,10 +6065,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119669392</v>
+        <v>119669112</v>
       </c>
       <c r="B51" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6090,21 +6081,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6121,10 +6112,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700529</v>
+        <v>700539</v>
       </c>
       <c r="R51" t="n">
-        <v>7283801</v>
+        <v>7283665</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6184,10 +6175,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119670567</v>
+        <v>119671571</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6196,25 +6187,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6231,10 +6222,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700267</v>
+        <v>700318</v>
       </c>
       <c r="R52" t="n">
-        <v>7283939</v>
+        <v>7283782</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6294,10 +6285,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119668728</v>
+        <v>119670358</v>
       </c>
       <c r="B53" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6310,21 +6301,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6341,10 +6332,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700480</v>
+        <v>700315</v>
       </c>
       <c r="R53" t="n">
-        <v>7283482</v>
+        <v>7283907</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6404,10 +6395,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119668966</v>
+        <v>119668701</v>
       </c>
       <c r="B54" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6420,28 +6411,24 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6455,10 +6442,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700497</v>
+        <v>700485</v>
       </c>
       <c r="R54" t="n">
-        <v>7283615</v>
+        <v>7283480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6518,10 +6505,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119670746</v>
+        <v>119668709</v>
       </c>
       <c r="B55" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6534,21 +6521,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6565,10 +6552,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700272</v>
+        <v>700480</v>
       </c>
       <c r="R55" t="n">
-        <v>7283984</v>
+        <v>7283480</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6628,10 +6615,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119669590</v>
+        <v>119670767</v>
       </c>
       <c r="B56" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6640,25 +6627,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6675,10 +6662,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700511</v>
+        <v>700279</v>
       </c>
       <c r="R56" t="n">
-        <v>7283834</v>
+        <v>7283983</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6738,10 +6725,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119671069</v>
+        <v>119670911</v>
       </c>
       <c r="B57" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6750,25 +6737,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6785,10 +6772,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700296</v>
+        <v>700271</v>
       </c>
       <c r="R57" t="n">
-        <v>7284015</v>
+        <v>7283996</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6848,7 +6835,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119669503</v>
+        <v>119669688</v>
       </c>
       <c r="B58" t="n">
         <v>91840</v>
@@ -6895,10 +6882,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700527</v>
+        <v>700487</v>
       </c>
       <c r="R58" t="n">
-        <v>7283820</v>
+        <v>7283810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6958,10 +6945,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119669445</v>
+        <v>119669000</v>
       </c>
       <c r="B59" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6970,25 +6957,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7005,10 +6992,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700524</v>
+        <v>700509</v>
       </c>
       <c r="R59" t="n">
-        <v>7283812</v>
+        <v>7283621</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7068,7 +7055,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119671618</v>
+        <v>119670970</v>
       </c>
       <c r="B60" t="n">
         <v>91840</v>
@@ -7115,10 +7102,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700324</v>
+        <v>700273</v>
       </c>
       <c r="R60" t="n">
-        <v>7283744</v>
+        <v>7283993</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7288,7 +7275,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119669670</v>
+        <v>119670438</v>
       </c>
       <c r="B62" t="n">
         <v>91840</v>
@@ -7335,10 +7322,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700494</v>
+        <v>700274</v>
       </c>
       <c r="R62" t="n">
-        <v>7283824</v>
+        <v>7283915</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7398,10 +7385,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119669337</v>
+        <v>119670220</v>
       </c>
       <c r="B63" t="n">
-        <v>92030</v>
+        <v>91852</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7410,25 +7397,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7445,10 +7432,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700544</v>
+        <v>700396</v>
       </c>
       <c r="R63" t="n">
-        <v>7283794</v>
+        <v>7283874</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7508,10 +7495,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119670772</v>
+        <v>119670129</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7520,25 +7507,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7555,10 +7542,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700279</v>
+        <v>700456</v>
       </c>
       <c r="R64" t="n">
-        <v>7283983</v>
+        <v>7283838</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7618,7 +7605,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119671393</v>
+        <v>119671624</v>
       </c>
       <c r="B65" t="n">
         <v>91840</v>
@@ -7665,10 +7652,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700329</v>
+        <v>700323</v>
       </c>
       <c r="R65" t="n">
-        <v>7284010</v>
+        <v>7283739</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7728,10 +7715,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119671608</v>
+        <v>119670490</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7740,25 +7727,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7775,10 +7762,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700327</v>
+        <v>700275</v>
       </c>
       <c r="R66" t="n">
-        <v>7283760</v>
+        <v>7283925</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7948,10 +7935,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119670129</v>
+        <v>119668875</v>
       </c>
       <c r="B68" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7960,25 +7947,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7995,10 +7982,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700456</v>
+        <v>700491</v>
       </c>
       <c r="R68" t="n">
-        <v>7283838</v>
+        <v>7283580</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8058,10 +8045,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119670794</v>
+        <v>119668829</v>
       </c>
       <c r="B69" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8070,25 +8057,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8105,10 +8092,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700259</v>
+        <v>700478</v>
       </c>
       <c r="R69" t="n">
-        <v>7283993</v>
+        <v>7283522</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8168,10 +8155,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119670438</v>
+        <v>119670256</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8184,21 +8171,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8215,10 +8202,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700274</v>
+        <v>700334</v>
       </c>
       <c r="R70" t="n">
-        <v>7283915</v>
+        <v>7283862</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8278,10 +8265,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119671219</v>
+        <v>119669634</v>
       </c>
       <c r="B71" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8290,25 +8277,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8325,10 +8312,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700316</v>
+        <v>700503</v>
       </c>
       <c r="R71" t="n">
-        <v>7284044</v>
+        <v>7283829</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8388,10 +8375,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119670801</v>
+        <v>119668736</v>
       </c>
       <c r="B72" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8400,25 +8387,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8435,10 +8422,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700262</v>
+        <v>700474</v>
       </c>
       <c r="R72" t="n">
-        <v>7283995</v>
+        <v>7283486</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8498,10 +8485,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119671327</v>
+        <v>119668926</v>
       </c>
       <c r="B73" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8514,21 +8501,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8545,10 +8532,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700332</v>
+        <v>700502</v>
       </c>
       <c r="R73" t="n">
-        <v>7284034</v>
+        <v>7283590</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8608,10 +8595,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119669000</v>
+        <v>119668092</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8620,25 +8607,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8655,10 +8642,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700509</v>
+        <v>700436</v>
       </c>
       <c r="R74" t="n">
-        <v>7283621</v>
+        <v>7283456</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8718,10 +8705,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119668797</v>
+        <v>119670998</v>
       </c>
       <c r="B75" t="n">
-        <v>91883</v>
+        <v>91832</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8734,21 +8721,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8765,10 +8752,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700473</v>
+        <v>700286</v>
       </c>
       <c r="R75" t="n">
-        <v>7283509</v>
+        <v>7283999</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8801,11 +8788,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Under gammal tallåga!</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8833,10 +8815,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119669350</v>
+        <v>119669042</v>
       </c>
       <c r="B76" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8849,21 +8831,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8880,10 +8862,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700547</v>
+        <v>700479</v>
       </c>
       <c r="R76" t="n">
-        <v>7283799</v>
+        <v>7283639</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8943,7 +8925,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119668423</v>
+        <v>119671088</v>
       </c>
       <c r="B77" t="n">
         <v>91832</v>
@@ -8990,10 +8972,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700431</v>
+        <v>700306</v>
       </c>
       <c r="R77" t="n">
-        <v>7283462</v>
+        <v>7283997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9053,10 +9035,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119670645</v>
+        <v>119669350</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9065,25 +9047,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9100,10 +9082,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700279</v>
+        <v>700547</v>
       </c>
       <c r="R78" t="n">
-        <v>7283952</v>
+        <v>7283799</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9163,7 +9145,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119668875</v>
+        <v>119670717</v>
       </c>
       <c r="B79" t="n">
         <v>91840</v>
@@ -9210,10 +9192,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700491</v>
+        <v>700303</v>
       </c>
       <c r="R79" t="n">
-        <v>7283580</v>
+        <v>7283965</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9273,7 +9255,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119668829</v>
+        <v>119668809</v>
       </c>
       <c r="B80" t="n">
         <v>91840</v>
@@ -9320,10 +9302,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700478</v>
+        <v>700481</v>
       </c>
       <c r="R80" t="n">
-        <v>7283522</v>
+        <v>7283509</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9383,10 +9365,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119669143</v>
+        <v>119669320</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9399,21 +9381,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9430,10 +9412,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700542</v>
+        <v>700590</v>
       </c>
       <c r="R81" t="n">
-        <v>7283681</v>
+        <v>7283790</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9493,10 +9475,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119670540</v>
+        <v>119671069</v>
       </c>
       <c r="B82" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9505,25 +9487,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9540,10 +9522,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700270</v>
+        <v>700296</v>
       </c>
       <c r="R82" t="n">
-        <v>7283931</v>
+        <v>7284015</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9603,10 +9585,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119668926</v>
+        <v>119668945</v>
       </c>
       <c r="B83" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9615,25 +9597,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9650,10 +9632,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700502</v>
+        <v>700493</v>
       </c>
       <c r="R83" t="n">
-        <v>7283590</v>
+        <v>7283596</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9713,7 +9695,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119670283</v>
+        <v>119668715</v>
       </c>
       <c r="B84" t="n">
         <v>91840</v>
@@ -9760,10 +9742,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700326</v>
+        <v>700480</v>
       </c>
       <c r="R84" t="n">
-        <v>7283891</v>
+        <v>7283480</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9823,10 +9805,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119670998</v>
+        <v>119671646</v>
       </c>
       <c r="B85" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9839,21 +9821,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9870,10 +9852,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>700286</v>
+        <v>700327</v>
       </c>
       <c r="R85" t="n">
-        <v>7283999</v>
+        <v>7283730</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9933,10 +9915,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119668849</v>
+        <v>119668834</v>
       </c>
       <c r="B86" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9945,25 +9927,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9980,10 +9962,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>700480</v>
+        <v>700478</v>
       </c>
       <c r="R86" t="n">
-        <v>7283558</v>
+        <v>7283522</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10043,10 +10025,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119669515</v>
+        <v>119669063</v>
       </c>
       <c r="B87" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10059,21 +10041,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10090,10 +10072,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700532</v>
+        <v>700527</v>
       </c>
       <c r="R87" t="n">
-        <v>7283821</v>
+        <v>7283650</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10153,10 +10135,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119669038</v>
+        <v>119671327</v>
       </c>
       <c r="B88" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10165,25 +10147,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10200,10 +10182,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700479</v>
+        <v>700332</v>
       </c>
       <c r="R88" t="n">
-        <v>7283639</v>
+        <v>7284034</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10263,10 +10245,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119669106</v>
+        <v>119670430</v>
       </c>
       <c r="B89" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10275,25 +10257,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10310,10 +10292,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>700538</v>
+        <v>700280</v>
       </c>
       <c r="R89" t="n">
-        <v>7283663</v>
+        <v>7283905</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10373,10 +10355,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119670886</v>
+        <v>119668760</v>
       </c>
       <c r="B90" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10385,25 +10367,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10420,10 +10402,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>700264</v>
+        <v>700485</v>
       </c>
       <c r="R90" t="n">
-        <v>7283999</v>
+        <v>7283507</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10483,7 +10465,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119669297</v>
+        <v>119669476</v>
       </c>
       <c r="B91" t="n">
         <v>91840</v>
@@ -10530,10 +10512,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>700594</v>
+        <v>700537</v>
       </c>
       <c r="R91" t="n">
-        <v>7283740</v>
+        <v>7283817</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10593,10 +10575,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119671104</v>
+        <v>119668797</v>
       </c>
       <c r="B92" t="n">
-        <v>91832</v>
+        <v>91883</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10609,21 +10591,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10640,10 +10622,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>700299</v>
+        <v>700473</v>
       </c>
       <c r="R92" t="n">
-        <v>7284034</v>
+        <v>7283509</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10676,6 +10658,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Under gammal tallåga!</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10703,10 +10690,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119671451</v>
+        <v>119671117</v>
       </c>
       <c r="B93" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10719,21 +10706,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10750,10 +10737,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700295</v>
+        <v>700298</v>
       </c>
       <c r="R93" t="n">
-        <v>7283983</v>
+        <v>7284037</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10813,10 +10800,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119671571</v>
+        <v>119670851</v>
       </c>
       <c r="B94" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10829,21 +10816,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10860,10 +10847,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>700318</v>
+        <v>700262</v>
       </c>
       <c r="R94" t="n">
-        <v>7283782</v>
+        <v>7283995</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10923,10 +10910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119669149</v>
+        <v>119669071</v>
       </c>
       <c r="B95" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10935,25 +10922,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10970,10 +10957,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>700549</v>
+        <v>700531</v>
       </c>
       <c r="R95" t="n">
-        <v>7283677</v>
+        <v>7283655</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11033,10 +11020,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119668747</v>
+        <v>119671618</v>
       </c>
       <c r="B96" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11045,25 +11032,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11080,10 +11067,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>700491</v>
+        <v>700324</v>
       </c>
       <c r="R96" t="n">
-        <v>7283496</v>
+        <v>7283744</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11143,10 +11130,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119671635</v>
+        <v>119670153</v>
       </c>
       <c r="B97" t="n">
-        <v>91852</v>
+        <v>92030</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11155,25 +11142,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4366</v>
+        <v>2079</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11190,10 +11177,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>700317</v>
+        <v>700453</v>
       </c>
       <c r="R97" t="n">
-        <v>7283727</v>
+        <v>7283845</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11253,10 +11240,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119670959</v>
+        <v>119670645</v>
       </c>
       <c r="B98" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11265,25 +11252,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11300,10 +11287,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>700274</v>
+        <v>700279</v>
       </c>
       <c r="R98" t="n">
-        <v>7283995</v>
+        <v>7283952</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11363,10 +11350,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119669471</v>
+        <v>119670794</v>
       </c>
       <c r="B99" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11375,25 +11362,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11410,10 +11397,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>700537</v>
+        <v>700259</v>
       </c>
       <c r="R99" t="n">
-        <v>7283817</v>
+        <v>7283993</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11473,10 +11460,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119670430</v>
+        <v>119671463</v>
       </c>
       <c r="B100" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11485,25 +11472,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11520,10 +11507,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>700280</v>
+        <v>700292</v>
       </c>
       <c r="R100" t="n">
-        <v>7283905</v>
+        <v>7283983</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11583,10 +11570,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119669271</v>
+        <v>119670230</v>
       </c>
       <c r="B101" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11595,25 +11582,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11630,10 +11617,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>700583</v>
+        <v>700384</v>
       </c>
       <c r="R101" t="n">
-        <v>7283727</v>
+        <v>7283876</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11693,10 +11680,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119670596</v>
+        <v>119670567</v>
       </c>
       <c r="B102" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11705,25 +11692,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11740,10 +11727,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>700268</v>
+        <v>700267</v>
       </c>
       <c r="R102" t="n">
-        <v>7283952</v>
+        <v>7283939</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11803,7 +11790,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119668503</v>
+        <v>119670659</v>
       </c>
       <c r="B103" t="n">
         <v>91840</v>
@@ -11850,10 +11837,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>700436</v>
+        <v>700260</v>
       </c>
       <c r="R103" t="n">
-        <v>7283469</v>
+        <v>7283959</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11913,10 +11900,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119668593</v>
+        <v>119670346</v>
       </c>
       <c r="B104" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11929,21 +11916,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11960,10 +11947,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>700468</v>
+        <v>700323</v>
       </c>
       <c r="R104" t="n">
-        <v>7283473</v>
+        <v>7283904</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12023,10 +12010,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119670163</v>
+        <v>119669058</v>
       </c>
       <c r="B105" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12035,25 +12022,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12070,10 +12057,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>700444</v>
+        <v>700528</v>
       </c>
       <c r="R105" t="n">
-        <v>7283880</v>
+        <v>7283648</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12133,10 +12120,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119670470</v>
+        <v>119669399</v>
       </c>
       <c r="B106" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12145,25 +12132,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12180,10 +12167,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>700275</v>
+        <v>700529</v>
       </c>
       <c r="R106" t="n">
-        <v>7283925</v>
+        <v>7283801</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12243,10 +12230,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119669592</v>
+        <v>119670333</v>
       </c>
       <c r="B107" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12255,25 +12242,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12290,10 +12277,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>700511</v>
+        <v>700318</v>
       </c>
       <c r="R107" t="n">
-        <v>7283834</v>
+        <v>7283895</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12353,10 +12340,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119669112</v>
+        <v>119668636</v>
       </c>
       <c r="B108" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12365,28 +12352,32 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -12400,10 +12391,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>700539</v>
+        <v>700481</v>
       </c>
       <c r="R108" t="n">
-        <v>7283665</v>
+        <v>7283469</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12463,10 +12454,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119671597</v>
+        <v>119670458</v>
       </c>
       <c r="B109" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12475,25 +12466,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12510,10 +12501,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>700315</v>
+        <v>700272</v>
       </c>
       <c r="R109" t="n">
-        <v>7283776</v>
+        <v>7283921</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12573,10 +12564,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119668736</v>
+        <v>119669392</v>
       </c>
       <c r="B110" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12585,25 +12576,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12620,10 +12611,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>700474</v>
+        <v>700529</v>
       </c>
       <c r="R110" t="n">
-        <v>7283486</v>
+        <v>7283801</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12683,10 +12674,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119669688</v>
+        <v>119668728</v>
       </c>
       <c r="B111" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12695,25 +12686,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12730,10 +12721,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>700487</v>
+        <v>700480</v>
       </c>
       <c r="R111" t="n">
-        <v>7283810</v>
+        <v>7283482</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12793,10 +12784,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119670941</v>
+        <v>119669138</v>
       </c>
       <c r="B112" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12805,25 +12796,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12840,10 +12831,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>700274</v>
+        <v>700540</v>
       </c>
       <c r="R112" t="n">
-        <v>7283997</v>
+        <v>7283677</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12903,7 +12894,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119670670</v>
+        <v>119669297</v>
       </c>
       <c r="B113" t="n">
         <v>91840</v>
@@ -12950,10 +12941,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>700264</v>
+        <v>700594</v>
       </c>
       <c r="R113" t="n">
-        <v>7283977</v>
+        <v>7283740</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13013,7 +13004,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119670346</v>
+        <v>119671626</v>
       </c>
       <c r="B114" t="n">
         <v>91852</v>
@@ -13063,7 +13054,7 @@
         <v>700323</v>
       </c>
       <c r="R114" t="n">
-        <v>7283904</v>
+        <v>7283739</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13123,7 +13114,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119671053</v>
+        <v>119668075</v>
       </c>
       <c r="B115" t="n">
         <v>91840</v>
@@ -13170,10 +13161,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>700272</v>
+        <v>700436</v>
       </c>
       <c r="R115" t="n">
-        <v>7284020</v>
+        <v>7283449</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13233,10 +13224,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119670911</v>
+        <v>119669503</v>
       </c>
       <c r="B116" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13245,25 +13236,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13280,10 +13271,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>700271</v>
+        <v>700527</v>
       </c>
       <c r="R116" t="n">
-        <v>7283996</v>
+        <v>7283820</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13343,10 +13334,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119669320</v>
+        <v>119668593</v>
       </c>
       <c r="B117" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13359,21 +13350,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13390,10 +13381,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>700590</v>
+        <v>700468</v>
       </c>
       <c r="R117" t="n">
-        <v>7283790</v>
+        <v>7283473</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13453,10 +13444,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119670984</v>
+        <v>119669515</v>
       </c>
       <c r="B118" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13465,25 +13456,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13500,10 +13491,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>700278</v>
+        <v>700532</v>
       </c>
       <c r="R118" t="n">
-        <v>7283995</v>
+        <v>7283821</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13563,7 +13554,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119671431</v>
+        <v>119669430</v>
       </c>
       <c r="B119" t="n">
         <v>91840</v>
@@ -13610,10 +13601,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>700310</v>
+        <v>700515</v>
       </c>
       <c r="R119" t="n">
-        <v>7283984</v>
+        <v>7283808</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13673,10 +13664,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119669309</v>
+        <v>119670301</v>
       </c>
       <c r="B120" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13685,25 +13676,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13720,10 +13711,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>700595</v>
+        <v>700314</v>
       </c>
       <c r="R120" t="n">
-        <v>7283758</v>
+        <v>7283890</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13783,10 +13774,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119668598</v>
+        <v>119671451</v>
       </c>
       <c r="B121" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13799,21 +13790,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13830,10 +13821,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>700468</v>
+        <v>700295</v>
       </c>
       <c r="R121" t="n">
-        <v>7283473</v>
+        <v>7283983</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13893,10 +13884,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119668715</v>
+        <v>119670777</v>
       </c>
       <c r="B122" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13905,25 +13896,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13940,10 +13931,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>700480</v>
+        <v>700279</v>
       </c>
       <c r="R122" t="n">
-        <v>7283480</v>
+        <v>7283988</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14003,10 +13994,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119668573</v>
+        <v>119669149</v>
       </c>
       <c r="B123" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14015,25 +14006,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14050,10 +14041,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>700462</v>
+        <v>700549</v>
       </c>
       <c r="R123" t="n">
-        <v>7283460</v>
+        <v>7283677</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14113,10 +14104,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119670256</v>
+        <v>119668598</v>
       </c>
       <c r="B124" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14125,25 +14116,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14160,10 +14151,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>700334</v>
+        <v>700468</v>
       </c>
       <c r="R124" t="n">
-        <v>7283862</v>
+        <v>7283473</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14223,10 +14214,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119669063</v>
+        <v>119670941</v>
       </c>
       <c r="B125" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14235,25 +14226,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14270,10 +14261,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>700527</v>
+        <v>700274</v>
       </c>
       <c r="R125" t="n">
-        <v>7283650</v>
+        <v>7283997</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14333,10 +14324,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119670106</v>
+        <v>119669038</v>
       </c>
       <c r="B126" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14345,25 +14336,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14380,10 +14371,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>700463</v>
+        <v>700479</v>
       </c>
       <c r="R126" t="n">
-        <v>7283819</v>
+        <v>7283639</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14443,10 +14434,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119671583</v>
+        <v>119671159</v>
       </c>
       <c r="B127" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14455,25 +14446,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14490,10 +14481,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>700309</v>
+        <v>700313</v>
       </c>
       <c r="R127" t="n">
-        <v>7283778</v>
+        <v>7284032</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14553,10 +14544,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119670153</v>
+        <v>119671219</v>
       </c>
       <c r="B128" t="n">
-        <v>92030</v>
+        <v>91834</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14569,21 +14560,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14600,10 +14591,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>700453</v>
+        <v>700316</v>
       </c>
       <c r="R128" t="n">
-        <v>7283845</v>
+        <v>7284044</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14663,10 +14654,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119668701</v>
+        <v>119669147</v>
       </c>
       <c r="B129" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14679,21 +14670,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14710,10 +14701,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>700485</v>
+        <v>700546</v>
       </c>
       <c r="R129" t="n">
-        <v>7283480</v>
+        <v>7283682</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14773,10 +14764,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119671159</v>
+        <v>119668966</v>
       </c>
       <c r="B130" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14785,28 +14776,32 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -14820,10 +14815,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>700313</v>
+        <v>700497</v>
       </c>
       <c r="R130" t="n">
-        <v>7284032</v>
+        <v>7283615</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14883,10 +14878,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119671088</v>
+        <v>119671393</v>
       </c>
       <c r="B131" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14895,25 +14890,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14930,10 +14925,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>700306</v>
+        <v>700329</v>
       </c>
       <c r="R131" t="n">
-        <v>7283997</v>
+        <v>7284010</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14993,10 +14988,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119669066</v>
+        <v>119670119</v>
       </c>
       <c r="B132" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15005,25 +15000,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15040,10 +15035,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>700525</v>
+        <v>700452</v>
       </c>
       <c r="R132" t="n">
-        <v>7283654</v>
+        <v>7283825</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15103,10 +15098,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119671007</v>
+        <v>119671583</v>
       </c>
       <c r="B133" t="n">
-        <v>91832</v>
+        <v>90807</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15115,25 +15110,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4361</v>
+        <v>65</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15150,10 +15145,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>700286</v>
+        <v>700309</v>
       </c>
       <c r="R133" t="n">
-        <v>7284004</v>
+        <v>7283778</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15213,10 +15208,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119668075</v>
+        <v>119669337</v>
       </c>
       <c r="B134" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15225,25 +15220,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15260,10 +15255,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>700436</v>
+        <v>700544</v>
       </c>
       <c r="R134" t="n">
-        <v>7283449</v>
+        <v>7283794</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15323,10 +15318,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119669419</v>
+        <v>119668514</v>
       </c>
       <c r="B135" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15339,21 +15334,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15370,10 +15365,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>700519</v>
+        <v>700458</v>
       </c>
       <c r="R135" t="n">
-        <v>7283805</v>
+        <v>7283459</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15433,7 +15428,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119670970</v>
+        <v>119670772</v>
       </c>
       <c r="B136" t="n">
         <v>91840</v>
@@ -15480,10 +15475,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>700273</v>
+        <v>700279</v>
       </c>
       <c r="R136" t="n">
-        <v>7283993</v>
+        <v>7283983</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15543,10 +15538,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119670230</v>
+        <v>119670886</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15555,25 +15550,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15590,10 +15585,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>700384</v>
+        <v>700264</v>
       </c>
       <c r="R137" t="n">
-        <v>7283876</v>
+        <v>7283999</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15653,7 +15648,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119670767</v>
+        <v>119671007</v>
       </c>
       <c r="B138" t="n">
         <v>91832</v>
@@ -15700,10 +15695,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>700279</v>
+        <v>700286</v>
       </c>
       <c r="R138" t="n">
-        <v>7283983</v>
+        <v>7284004</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15763,7 +15758,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119669683</v>
+        <v>119668849</v>
       </c>
       <c r="B139" t="n">
         <v>91840</v>
@@ -15810,10 +15805,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>700488</v>
+        <v>700480</v>
       </c>
       <c r="R139" t="n">
-        <v>7283816</v>
+        <v>7283558</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15873,10 +15868,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119669147</v>
+        <v>119669620</v>
       </c>
       <c r="B140" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15885,25 +15880,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15920,10 +15915,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>700546</v>
+        <v>700508</v>
       </c>
       <c r="R140" t="n">
-        <v>7283682</v>
+        <v>7283824</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15983,10 +15978,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119669674</v>
+        <v>119671635</v>
       </c>
       <c r="B141" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15995,25 +15990,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16030,10 +16025,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>700494</v>
+        <v>700317</v>
       </c>
       <c r="R141" t="n">
-        <v>7283824</v>
+        <v>7283727</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16093,10 +16088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119670580</v>
+        <v>119670163</v>
       </c>
       <c r="B142" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16109,21 +16104,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16140,10 +16135,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>700268</v>
+        <v>700444</v>
       </c>
       <c r="R142" t="n">
-        <v>7283948</v>
+        <v>7283880</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16203,10 +16198,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119669042</v>
+        <v>119668423</v>
       </c>
       <c r="B143" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16219,21 +16214,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16250,10 +16245,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>700479</v>
+        <v>700431</v>
       </c>
       <c r="R143" t="n">
-        <v>7283639</v>
+        <v>7283462</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16313,7 +16308,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119669410</v>
+        <v>119670195</v>
       </c>
       <c r="B144" t="n">
         <v>91834</v>
@@ -16360,10 +16355,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>700511</v>
+        <v>700444</v>
       </c>
       <c r="R144" t="n">
-        <v>7283802</v>
+        <v>7283887</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16423,10 +16418,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119668809</v>
+        <v>119669271</v>
       </c>
       <c r="B145" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16435,25 +16430,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16470,10 +16465,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>700481</v>
+        <v>700583</v>
       </c>
       <c r="R145" t="n">
-        <v>7283509</v>
+        <v>7283727</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16533,10 +16528,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119669138</v>
+        <v>119671104</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16545,25 +16540,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16580,10 +16575,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>700540</v>
+        <v>700299</v>
       </c>
       <c r="R146" t="n">
-        <v>7283677</v>
+        <v>7284034</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16643,10 +16638,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119669524</v>
+        <v>119670865</v>
       </c>
       <c r="B147" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16655,25 +16650,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16690,10 +16685,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>700534</v>
+        <v>700262</v>
       </c>
       <c r="R147" t="n">
-        <v>7283826</v>
+        <v>7284000</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16753,10 +16748,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119669634</v>
+        <v>119671608</v>
       </c>
       <c r="B148" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16769,21 +16764,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16800,10 +16795,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>700503</v>
+        <v>700327</v>
       </c>
       <c r="R148" t="n">
-        <v>7283829</v>
+        <v>7283760</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16863,10 +16858,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119670259</v>
+        <v>119669380</v>
       </c>
       <c r="B149" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16879,21 +16874,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16910,10 +16905,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>700337</v>
+        <v>700532</v>
       </c>
       <c r="R149" t="n">
-        <v>7283884</v>
+        <v>7283795</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16973,10 +16968,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119671138</v>
+        <v>119670372</v>
       </c>
       <c r="B150" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16985,25 +16980,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17020,10 +17015,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>700311</v>
+        <v>700297</v>
       </c>
       <c r="R150" t="n">
-        <v>7284032</v>
+        <v>7283911</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17056,6 +17051,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>under gammal tallåga</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17083,7 +17083,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119668945</v>
+        <v>119669670</v>
       </c>
       <c r="B151" t="n">
         <v>91840</v>
@@ -17130,10 +17130,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>700493</v>
+        <v>700494</v>
       </c>
       <c r="R151" t="n">
-        <v>7283596</v>
+        <v>7283824</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17193,10 +17193,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119670490</v>
+        <v>119669250</v>
       </c>
       <c r="B152" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17205,25 +17205,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17240,10 +17240,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>700275</v>
+        <v>700565</v>
       </c>
       <c r="R152" t="n">
-        <v>7283925</v>
+        <v>7283709</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119669592</v>
+        <v>119668573</v>
       </c>
       <c r="B4" t="n">
         <v>91840</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700511</v>
+        <v>700462</v>
       </c>
       <c r="R4" t="n">
-        <v>7283834</v>
+        <v>7283460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119668503</v>
+        <v>119668856</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700436</v>
+        <v>700493</v>
       </c>
       <c r="R5" t="n">
-        <v>7283469</v>
+        <v>7283574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119669590</v>
+        <v>119671053</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700511</v>
+        <v>700272</v>
       </c>
       <c r="R6" t="n">
-        <v>7283834</v>
+        <v>7284020</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119668910</v>
+        <v>119670984</v>
       </c>
       <c r="B7" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700502</v>
+        <v>700278</v>
       </c>
       <c r="R7" t="n">
-        <v>7283590</v>
+        <v>7283995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119668573</v>
+        <v>119669592</v>
       </c>
       <c r="B8" t="n">
         <v>91840</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700462</v>
+        <v>700511</v>
       </c>
       <c r="R8" t="n">
-        <v>7283460</v>
+        <v>7283834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119668856</v>
+        <v>119668503</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,25 +1457,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700493</v>
+        <v>700436</v>
       </c>
       <c r="R9" t="n">
-        <v>7283574</v>
+        <v>7283469</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119671053</v>
+        <v>119669590</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700272</v>
+        <v>700511</v>
       </c>
       <c r="R10" t="n">
-        <v>7284020</v>
+        <v>7283834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119670984</v>
+        <v>119668910</v>
       </c>
       <c r="B11" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700278</v>
+        <v>700502</v>
       </c>
       <c r="R11" t="n">
-        <v>7283995</v>
+        <v>7283590</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -15318,10 +15318,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119668514</v>
+        <v>119668849</v>
       </c>
       <c r="B135" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15330,25 +15330,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15365,10 +15365,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>700458</v>
+        <v>700480</v>
       </c>
       <c r="R135" t="n">
-        <v>7283459</v>
+        <v>7283558</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15428,10 +15428,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119670772</v>
+        <v>119669620</v>
       </c>
       <c r="B136" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15444,21 +15444,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15475,10 +15475,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>700279</v>
+        <v>700508</v>
       </c>
       <c r="R136" t="n">
-        <v>7283983</v>
+        <v>7283824</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15538,10 +15538,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119670886</v>
+        <v>119671635</v>
       </c>
       <c r="B137" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15550,25 +15550,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15585,10 +15585,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>700264</v>
+        <v>700317</v>
       </c>
       <c r="R137" t="n">
-        <v>7283999</v>
+        <v>7283727</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15648,10 +15648,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119671007</v>
+        <v>119670163</v>
       </c>
       <c r="B138" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15664,21 +15664,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15695,10 +15695,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>700286</v>
+        <v>700444</v>
       </c>
       <c r="R138" t="n">
-        <v>7284004</v>
+        <v>7283880</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15758,10 +15758,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119668849</v>
+        <v>119668514</v>
       </c>
       <c r="B139" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15770,25 +15770,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15805,10 +15805,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>700480</v>
+        <v>700458</v>
       </c>
       <c r="R139" t="n">
-        <v>7283558</v>
+        <v>7283459</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15868,10 +15868,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119669620</v>
+        <v>119670772</v>
       </c>
       <c r="B140" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15884,21 +15884,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15915,10 +15915,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>700508</v>
+        <v>700279</v>
       </c>
       <c r="R140" t="n">
-        <v>7283824</v>
+        <v>7283983</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15978,10 +15978,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119671635</v>
+        <v>119670886</v>
       </c>
       <c r="B141" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15990,25 +15990,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16025,10 +16025,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>700317</v>
+        <v>700264</v>
       </c>
       <c r="R141" t="n">
-        <v>7283727</v>
+        <v>7283999</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16088,10 +16088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119670163</v>
+        <v>119671007</v>
       </c>
       <c r="B142" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16104,21 +16104,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>700444</v>
+        <v>700286</v>
       </c>
       <c r="R142" t="n">
-        <v>7283880</v>
+        <v>7284004</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119668573</v>
+        <v>119669592</v>
       </c>
       <c r="B4" t="n">
         <v>91840</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700462</v>
+        <v>700511</v>
       </c>
       <c r="R4" t="n">
-        <v>7283460</v>
+        <v>7283834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119668856</v>
+        <v>119668503</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700493</v>
+        <v>700436</v>
       </c>
       <c r="R5" t="n">
-        <v>7283574</v>
+        <v>7283469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119671053</v>
+        <v>119669590</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700272</v>
+        <v>700511</v>
       </c>
       <c r="R6" t="n">
-        <v>7284020</v>
+        <v>7283834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119670984</v>
+        <v>119668910</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700278</v>
+        <v>700502</v>
       </c>
       <c r="R7" t="n">
-        <v>7283995</v>
+        <v>7283590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119669592</v>
+        <v>119668573</v>
       </c>
       <c r="B8" t="n">
         <v>91840</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700511</v>
+        <v>700462</v>
       </c>
       <c r="R8" t="n">
-        <v>7283834</v>
+        <v>7283460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119668503</v>
+        <v>119668856</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,25 +1457,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700436</v>
+        <v>700493</v>
       </c>
       <c r="R9" t="n">
-        <v>7283469</v>
+        <v>7283574</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119669590</v>
+        <v>119671053</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700511</v>
+        <v>700272</v>
       </c>
       <c r="R10" t="n">
-        <v>7283834</v>
+        <v>7284020</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119668910</v>
+        <v>119670984</v>
       </c>
       <c r="B11" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700502</v>
+        <v>700278</v>
       </c>
       <c r="R11" t="n">
-        <v>7283590</v>
+        <v>7283995</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119669410</v>
+        <v>119670237</v>
       </c>
       <c r="B22" t="n">
         <v>91834</v>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700511</v>
+        <v>700384</v>
       </c>
       <c r="R22" t="n">
-        <v>7283802</v>
+        <v>7283876</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119670237</v>
+        <v>119669410</v>
       </c>
       <c r="B23" t="n">
         <v>91834</v>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700384</v>
+        <v>700511</v>
       </c>
       <c r="R23" t="n">
-        <v>7283876</v>
+        <v>7283802</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -10690,10 +10690,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119671117</v>
+        <v>119670153</v>
       </c>
       <c r="B93" t="n">
-        <v>91832</v>
+        <v>92030</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10706,21 +10706,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4361</v>
+        <v>2079</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10737,10 +10737,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700298</v>
+        <v>700453</v>
       </c>
       <c r="R93" t="n">
-        <v>7284037</v>
+        <v>7283845</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10800,7 +10800,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119670851</v>
+        <v>119671117</v>
       </c>
       <c r="B94" t="n">
         <v>91832</v>
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>700262</v>
+        <v>700298</v>
       </c>
       <c r="R94" t="n">
-        <v>7283995</v>
+        <v>7284037</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10910,10 +10910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119669071</v>
+        <v>119670851</v>
       </c>
       <c r="B95" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10922,25 +10922,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>700531</v>
+        <v>700262</v>
       </c>
       <c r="R95" t="n">
-        <v>7283655</v>
+        <v>7283995</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11020,7 +11020,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119671618</v>
+        <v>119669071</v>
       </c>
       <c r="B96" t="n">
         <v>91840</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>700324</v>
+        <v>700531</v>
       </c>
       <c r="R96" t="n">
-        <v>7283744</v>
+        <v>7283655</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11130,10 +11130,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119670153</v>
+        <v>119671618</v>
       </c>
       <c r="B97" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11142,25 +11142,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11177,10 +11177,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>700453</v>
+        <v>700324</v>
       </c>
       <c r="R97" t="n">
-        <v>7283845</v>
+        <v>7283744</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13334,10 +13334,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119668593</v>
+        <v>119670777</v>
       </c>
       <c r="B117" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13346,25 +13346,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>700468</v>
+        <v>700279</v>
       </c>
       <c r="R117" t="n">
-        <v>7283473</v>
+        <v>7283988</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13444,10 +13444,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119669515</v>
+        <v>119668593</v>
       </c>
       <c r="B118" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13460,21 +13460,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13491,10 +13491,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>700532</v>
+        <v>700468</v>
       </c>
       <c r="R118" t="n">
-        <v>7283821</v>
+        <v>7283473</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13884,10 +13884,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119670777</v>
+        <v>119669515</v>
       </c>
       <c r="B122" t="n">
-        <v>92030</v>
+        <v>91852</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13896,25 +13896,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2079</v>
+        <v>4366</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13931,10 +13931,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>700279</v>
+        <v>700532</v>
       </c>
       <c r="R122" t="n">
-        <v>7283988</v>
+        <v>7283821</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -2875,7 +2875,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119670237</v>
+        <v>119669410</v>
       </c>
       <c r="B22" t="n">
         <v>91834</v>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700384</v>
+        <v>700511</v>
       </c>
       <c r="R22" t="n">
-        <v>7283876</v>
+        <v>7283802</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119669410</v>
+        <v>119670237</v>
       </c>
       <c r="B23" t="n">
         <v>91834</v>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700511</v>
+        <v>700384</v>
       </c>
       <c r="R23" t="n">
-        <v>7283802</v>
+        <v>7283876</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -6285,10 +6285,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119670358</v>
+        <v>119670767</v>
       </c>
       <c r="B53" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6301,21 +6301,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700315</v>
+        <v>700279</v>
       </c>
       <c r="R53" t="n">
-        <v>7283907</v>
+        <v>7283983</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119668701</v>
+        <v>119670911</v>
       </c>
       <c r="B54" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6411,21 +6411,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700485</v>
+        <v>700271</v>
       </c>
       <c r="R54" t="n">
-        <v>7283480</v>
+        <v>7283996</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119668709</v>
+        <v>119669688</v>
       </c>
       <c r="B55" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6517,25 +6517,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6552,10 +6552,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700480</v>
+        <v>700487</v>
       </c>
       <c r="R55" t="n">
-        <v>7283480</v>
+        <v>7283810</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6615,10 +6615,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119670767</v>
+        <v>119669000</v>
       </c>
       <c r="B56" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6627,25 +6627,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700279</v>
+        <v>700509</v>
       </c>
       <c r="R56" t="n">
-        <v>7283983</v>
+        <v>7283621</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119670911</v>
+        <v>119670970</v>
       </c>
       <c r="B57" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6737,25 +6737,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700271</v>
+        <v>700273</v>
       </c>
       <c r="R57" t="n">
-        <v>7283996</v>
+        <v>7283993</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6835,10 +6835,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119669688</v>
+        <v>119669004</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6851,21 +6851,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6882,10 +6882,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700487</v>
+        <v>700498</v>
       </c>
       <c r="R58" t="n">
-        <v>7283810</v>
+        <v>7283624</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6945,7 +6945,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119669000</v>
+        <v>119670438</v>
       </c>
       <c r="B59" t="n">
         <v>91840</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700509</v>
+        <v>700274</v>
       </c>
       <c r="R59" t="n">
-        <v>7283621</v>
+        <v>7283915</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7055,10 +7055,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119670970</v>
+        <v>119670220</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7071,21 +7071,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700273</v>
+        <v>700396</v>
       </c>
       <c r="R60" t="n">
-        <v>7283993</v>
+        <v>7283874</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119669004</v>
+        <v>119670358</v>
       </c>
       <c r="B61" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7177,25 +7177,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7212,10 +7212,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700498</v>
+        <v>700315</v>
       </c>
       <c r="R61" t="n">
-        <v>7283624</v>
+        <v>7283907</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7275,10 +7275,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119670438</v>
+        <v>119668701</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7287,25 +7287,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700274</v>
+        <v>700485</v>
       </c>
       <c r="R62" t="n">
-        <v>7283915</v>
+        <v>7283480</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7385,10 +7385,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119670220</v>
+        <v>119668709</v>
       </c>
       <c r="B63" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7397,25 +7397,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700396</v>
+        <v>700480</v>
       </c>
       <c r="R63" t="n">
-        <v>7283874</v>
+        <v>7283480</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -14324,10 +14324,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119669038</v>
+        <v>119671159</v>
       </c>
       <c r="B126" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14340,21 +14340,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14371,10 +14371,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>700479</v>
+        <v>700313</v>
       </c>
       <c r="R126" t="n">
-        <v>7283639</v>
+        <v>7284032</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14434,10 +14434,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119671159</v>
+        <v>119669038</v>
       </c>
       <c r="B127" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14450,21 +14450,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14481,10 +14481,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>700313</v>
+        <v>700479</v>
       </c>
       <c r="R127" t="n">
-        <v>7284032</v>
+        <v>7283639</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15208,10 +15208,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119669337</v>
+        <v>119668514</v>
       </c>
       <c r="B134" t="n">
-        <v>92030</v>
+        <v>91834</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15224,21 +15224,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15255,10 +15255,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>700544</v>
+        <v>700458</v>
       </c>
       <c r="R134" t="n">
-        <v>7283794</v>
+        <v>7283459</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15428,10 +15428,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119669620</v>
+        <v>119670163</v>
       </c>
       <c r="B136" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15440,25 +15440,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15475,10 +15475,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>700508</v>
+        <v>700444</v>
       </c>
       <c r="R136" t="n">
-        <v>7283824</v>
+        <v>7283880</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15538,10 +15538,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119671635</v>
+        <v>119671007</v>
       </c>
       <c r="B137" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15550,25 +15550,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15585,10 +15585,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>700317</v>
+        <v>700286</v>
       </c>
       <c r="R137" t="n">
-        <v>7283727</v>
+        <v>7284004</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15648,10 +15648,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119670163</v>
+        <v>119669620</v>
       </c>
       <c r="B138" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15660,25 +15660,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15695,10 +15695,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>700444</v>
+        <v>700508</v>
       </c>
       <c r="R138" t="n">
-        <v>7283880</v>
+        <v>7283824</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15758,10 +15758,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119668514</v>
+        <v>119669337</v>
       </c>
       <c r="B139" t="n">
-        <v>91834</v>
+        <v>92030</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15774,21 +15774,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15805,10 +15805,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>700458</v>
+        <v>700544</v>
       </c>
       <c r="R139" t="n">
-        <v>7283459</v>
+        <v>7283794</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15868,10 +15868,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119670772</v>
+        <v>119670886</v>
       </c>
       <c r="B140" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15880,25 +15880,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15915,10 +15915,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>700279</v>
+        <v>700264</v>
       </c>
       <c r="R140" t="n">
-        <v>7283983</v>
+        <v>7283999</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15978,10 +15978,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119670886</v>
+        <v>119670772</v>
       </c>
       <c r="B141" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15990,25 +15990,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16025,10 +16025,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>700264</v>
+        <v>700279</v>
       </c>
       <c r="R141" t="n">
-        <v>7283999</v>
+        <v>7283983</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16088,10 +16088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119671007</v>
+        <v>119671635</v>
       </c>
       <c r="B142" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16100,25 +16100,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>700286</v>
+        <v>700317</v>
       </c>
       <c r="R142" t="n">
-        <v>7284004</v>
+        <v>7283727</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -4745,10 +4745,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119668690</v>
+        <v>119670580</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4757,25 +4757,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700485</v>
+        <v>700268</v>
       </c>
       <c r="R39" t="n">
-        <v>7283480</v>
+        <v>7283948</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119668747</v>
+        <v>119668690</v>
       </c>
       <c r="B40" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4867,25 +4867,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700491</v>
+        <v>700485</v>
       </c>
       <c r="R40" t="n">
-        <v>7283496</v>
+        <v>7283480</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4965,7 +4965,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119669106</v>
+        <v>119668747</v>
       </c>
       <c r="B41" t="n">
         <v>91834</v>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700538</v>
+        <v>700491</v>
       </c>
       <c r="R41" t="n">
-        <v>7283663</v>
+        <v>7283496</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119669073</v>
+        <v>119669106</v>
       </c>
       <c r="B42" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5091,21 +5091,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700531</v>
+        <v>700538</v>
       </c>
       <c r="R42" t="n">
-        <v>7283655</v>
+        <v>7283663</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119670540</v>
+        <v>119669073</v>
       </c>
       <c r="B43" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5201,21 +5201,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700270</v>
+        <v>700531</v>
       </c>
       <c r="R43" t="n">
-        <v>7283931</v>
+        <v>7283655</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5295,10 +5295,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119670580</v>
+        <v>119670540</v>
       </c>
       <c r="B44" t="n">
-        <v>89633</v>
+        <v>91832</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5311,21 +5311,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700268</v>
+        <v>700270</v>
       </c>
       <c r="R44" t="n">
-        <v>7283948</v>
+        <v>7283931</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6285,10 +6285,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119670767</v>
+        <v>119670358</v>
       </c>
       <c r="B53" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6301,21 +6301,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700279</v>
+        <v>700315</v>
       </c>
       <c r="R53" t="n">
-        <v>7283983</v>
+        <v>7283907</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119670911</v>
+        <v>119668701</v>
       </c>
       <c r="B54" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6411,21 +6411,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700271</v>
+        <v>700485</v>
       </c>
       <c r="R54" t="n">
-        <v>7283996</v>
+        <v>7283480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119669688</v>
+        <v>119668709</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6517,25 +6517,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6552,10 +6552,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700487</v>
+        <v>700480</v>
       </c>
       <c r="R55" t="n">
-        <v>7283810</v>
+        <v>7283480</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6615,10 +6615,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119669000</v>
+        <v>119670767</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6627,25 +6627,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700509</v>
+        <v>700279</v>
       </c>
       <c r="R56" t="n">
-        <v>7283621</v>
+        <v>7283983</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119670970</v>
+        <v>119670911</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6737,25 +6737,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700273</v>
+        <v>700271</v>
       </c>
       <c r="R57" t="n">
-        <v>7283993</v>
+        <v>7283996</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6835,10 +6835,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119669004</v>
+        <v>119669688</v>
       </c>
       <c r="B58" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6851,21 +6851,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6882,10 +6882,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700498</v>
+        <v>700487</v>
       </c>
       <c r="R58" t="n">
-        <v>7283624</v>
+        <v>7283810</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6945,7 +6945,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119670438</v>
+        <v>119669000</v>
       </c>
       <c r="B59" t="n">
         <v>91840</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700274</v>
+        <v>700509</v>
       </c>
       <c r="R59" t="n">
-        <v>7283915</v>
+        <v>7283621</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7055,10 +7055,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119670220</v>
+        <v>119670970</v>
       </c>
       <c r="B60" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7071,21 +7071,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700396</v>
+        <v>700273</v>
       </c>
       <c r="R60" t="n">
-        <v>7283874</v>
+        <v>7283993</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119670358</v>
+        <v>119669004</v>
       </c>
       <c r="B61" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7177,25 +7177,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7212,10 +7212,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700315</v>
+        <v>700498</v>
       </c>
       <c r="R61" t="n">
-        <v>7283907</v>
+        <v>7283624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7275,10 +7275,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119668701</v>
+        <v>119670438</v>
       </c>
       <c r="B62" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7287,25 +7287,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700485</v>
+        <v>700274</v>
       </c>
       <c r="R62" t="n">
-        <v>7283480</v>
+        <v>7283915</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7385,10 +7385,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119668709</v>
+        <v>119670220</v>
       </c>
       <c r="B63" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7397,25 +7397,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700480</v>
+        <v>700396</v>
       </c>
       <c r="R63" t="n">
-        <v>7283480</v>
+        <v>7283874</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -10690,10 +10690,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119670153</v>
+        <v>119671117</v>
       </c>
       <c r="B93" t="n">
-        <v>92030</v>
+        <v>91832</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10706,21 +10706,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2079</v>
+        <v>4361</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10737,10 +10737,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700453</v>
+        <v>700298</v>
       </c>
       <c r="R93" t="n">
-        <v>7283845</v>
+        <v>7284037</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10800,7 +10800,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119671117</v>
+        <v>119670851</v>
       </c>
       <c r="B94" t="n">
         <v>91832</v>
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>700298</v>
+        <v>700262</v>
       </c>
       <c r="R94" t="n">
-        <v>7284037</v>
+        <v>7283995</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10910,10 +10910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119670851</v>
+        <v>119669071</v>
       </c>
       <c r="B95" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10922,25 +10922,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>700262</v>
+        <v>700531</v>
       </c>
       <c r="R95" t="n">
-        <v>7283995</v>
+        <v>7283655</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11020,7 +11020,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119669071</v>
+        <v>119671618</v>
       </c>
       <c r="B96" t="n">
         <v>91840</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>700531</v>
+        <v>700324</v>
       </c>
       <c r="R96" t="n">
-        <v>7283655</v>
+        <v>7283744</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11130,10 +11130,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119671618</v>
+        <v>119670153</v>
       </c>
       <c r="B97" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11142,25 +11142,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11177,10 +11177,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>700324</v>
+        <v>700453</v>
       </c>
       <c r="R97" t="n">
-        <v>7283744</v>
+        <v>7283845</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -14324,10 +14324,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119671159</v>
+        <v>119669038</v>
       </c>
       <c r="B126" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14340,21 +14340,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14371,10 +14371,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>700313</v>
+        <v>700479</v>
       </c>
       <c r="R126" t="n">
-        <v>7284032</v>
+        <v>7283639</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14434,10 +14434,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119669038</v>
+        <v>119671159</v>
       </c>
       <c r="B127" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14450,21 +14450,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14481,10 +14481,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>700479</v>
+        <v>700313</v>
       </c>
       <c r="R127" t="n">
-        <v>7283639</v>
+        <v>7284032</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15208,10 +15208,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119668514</v>
+        <v>119669337</v>
       </c>
       <c r="B134" t="n">
-        <v>91834</v>
+        <v>92030</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15224,21 +15224,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15255,10 +15255,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>700458</v>
+        <v>700544</v>
       </c>
       <c r="R134" t="n">
-        <v>7283459</v>
+        <v>7283794</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15428,10 +15428,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119670163</v>
+        <v>119669620</v>
       </c>
       <c r="B136" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15440,25 +15440,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15475,10 +15475,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>700444</v>
+        <v>700508</v>
       </c>
       <c r="R136" t="n">
-        <v>7283880</v>
+        <v>7283824</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15538,10 +15538,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119671007</v>
+        <v>119671635</v>
       </c>
       <c r="B137" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15550,25 +15550,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15585,10 +15585,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>700286</v>
+        <v>700317</v>
       </c>
       <c r="R137" t="n">
-        <v>7284004</v>
+        <v>7283727</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15648,10 +15648,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119669620</v>
+        <v>119670163</v>
       </c>
       <c r="B138" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15660,25 +15660,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15695,10 +15695,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>700508</v>
+        <v>700444</v>
       </c>
       <c r="R138" t="n">
-        <v>7283824</v>
+        <v>7283880</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15758,10 +15758,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119669337</v>
+        <v>119668514</v>
       </c>
       <c r="B139" t="n">
-        <v>92030</v>
+        <v>91834</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15774,21 +15774,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15805,10 +15805,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>700544</v>
+        <v>700458</v>
       </c>
       <c r="R139" t="n">
-        <v>7283794</v>
+        <v>7283459</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15868,10 +15868,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119670886</v>
+        <v>119670772</v>
       </c>
       <c r="B140" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15880,25 +15880,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15915,10 +15915,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>700264</v>
+        <v>700279</v>
       </c>
       <c r="R140" t="n">
-        <v>7283999</v>
+        <v>7283983</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15978,10 +15978,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119670772</v>
+        <v>119670886</v>
       </c>
       <c r="B141" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15990,25 +15990,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16025,10 +16025,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>700279</v>
+        <v>700264</v>
       </c>
       <c r="R141" t="n">
-        <v>7283983</v>
+        <v>7283999</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16088,10 +16088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119671635</v>
+        <v>119671007</v>
       </c>
       <c r="B142" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16100,25 +16100,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>700317</v>
+        <v>700286</v>
       </c>
       <c r="R142" t="n">
-        <v>7283727</v>
+        <v>7284004</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 3199-2024 artfynd.xlsx
+++ b/artfynd/A 3199-2024 artfynd.xlsx
@@ -4968,7 +4968,7 @@
         <v>119668747</v>
       </c>
       <c r="B41" t="n">
-        <v>91957</v>
+        <v>91967</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
